--- a/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
+++ b/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
@@ -2172,16 +2172,6 @@
         </is>
       </c>
       <c r="U26" s="6"/>
-      <c r="W26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10147 Crew pattern — 7 of 9 at a venue, this one says Warehouse: CREW PATTERN: 7 of 9 workers were at a venue on Mon 21 Sep 2026 (FNB Stadium, Fnb stadium) — Erick Mpho Molefe says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
-        </is>
-      </c>
-      <c r="X26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10147 STILL OPEN — no decision recorded yet (claimed hours used)</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
@@ -3748,12 +3738,12 @@
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9979 Manual overlap review: the same employee has another overlapping entry on 2026-09-21 for 07:00-16:00. | #10131 ALREADY PAID — SAME SHIFT AGAIN (duplicate): John was paid Mon 21 Sep 2026 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h × R95,00 = R855,00 (payroll 2026-09-19). He now claims 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h for the same day. Every hour of this claim is already paid. Nothing is due: R0,00. Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed. System recommended 0.00 h.</t>
+          <t xml:space="preserve">#10131 ALREADY PAID — SAME SHIFT AGAIN (duplicate): John was paid Mon 21 Sep 2026 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h × R95,00 = R855,00 (payroll 2026-09-19). He now claims 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h for the same day. Every hour of this claim is already paid. Nothing is due: R0,00. Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed. System recommended 0.00 h.</t>
         </is>
       </c>
       <c r="X45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9979 DECIDED 3.00 h by Bernie Burness 2026-09-23 09:01: ALREADY BILLED Monday 2026-09-21 · 07:00–16:00 · 9.00 h Normal · FNB Stadium · Strike down R855,00 · shift #9857 · in THIS payroll (2026-09-19 → 2026-09-25, not yet paid) | #10131 DECIDED 0.00 h by Bernie Burness 2026-09-23 09:03: Already paid — SAME SHIFT AGAIN (duplicate) — R0,00 still due — approved amount R0,00</t>
+          <t xml:space="preserve">#10131 DECIDED 0.00 h by Bernie Burness 2026-09-23 09:03: Already paid — SAME SHIFT AGAIN (duplicate) — R0,00 still due — approved amount R0,00</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8554,7 @@
         <v>500</v>
       </c>
       <c r="Y7" s="4">
-        <f>MAX(0,500-X7)</f>
+        <f>MAX(0,1000-X7)</f>
       </c>
       <c r="Z7" s="4">
         <f>U7+X7</f>
@@ -8734,7 +8724,7 @@
         <v>1000</v>
       </c>
       <c r="Y9" s="4">
-        <f>MAX(0,1100-X9)</f>
+        <f>MAX(0,1600-X9)</f>
       </c>
       <c r="Z9" s="4">
         <f>U9+X9</f>
@@ -11193,13 +11183,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN</t>
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
       <c r="B16" s="26">
-        <v>10147</v>
+        <v>10015</v>
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
@@ -11208,22 +11198,22 @@
       </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">07:00–16:00 warehouse</t>
         </is>
       </c>
       <c r="F16" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crew pattern — 7 of 9 at a venue, this one says Warehouse</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G16" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREW PATTERN: 7 of 9 workers were at a venue on Mon 21 Sep 2026 (FNB Stadium, Fnb stadium) — Erick Mpho Molefe says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H16" s="26"/>
@@ -11231,10 +11221,26 @@
         <v>9</v>
       </c>
       <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M16" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 06:40:17</t>
+        </is>
+      </c>
+      <c r="N16" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9800 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
@@ -11243,7 +11249,7 @@
         </is>
       </c>
       <c r="B17" s="26">
-        <v>10015</v>
+        <v>10010</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
@@ -11252,109 +11258,109 @@
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 warehouse</t>
+          <t xml:space="preserve">07:00–15:00 wharehouse</t>
         </is>
       </c>
       <c r="F17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Erick Mpho Molefe worked 07:00–16:00 on 2026-09-24 (Heritage Day) at wharehouse (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
         </is>
       </c>
       <c r="H17" s="26"/>
       <c r="I17" s="27">
-        <v>9</v>
-      </c>
-      <c r="J17" s="26"/>
+        <v>8</v>
+      </c>
+      <c r="J17" s="27">
+        <v>7.5</v>
+      </c>
       <c r="K17" s="26" t="inlineStr">
         <is>
+          <t xml:space="preserve">approve adjusted</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 10:29:03</t>
+        </is>
+      </c>
+      <c r="N17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B18" s="29">
+        <v>10073</v>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Givemore Chifetete Kuziwa</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–18:00 Warehouse</t>
+        </is>
+      </c>
+      <c r="F18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse claimed — but area says “Pretoria and fnb”</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAREHOUSE CLAIMED BUT AREA SAYS “Pretoria and fnb”: Givemore Chifetete Kuziwa selected Warehouse Team at “Warehouse” for 12.00 h on Thu 17 Sep 2026, but wrote the area as “Pretoria and fnb” — that is a venue, not the warehouse. Other workers were at Botanical garden Pretoria that day. If he was at “Pretoria and fnb”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+        </is>
+      </c>
+      <c r="H18" s="29"/>
+      <c r="I18" s="30">
+        <v>12</v>
+      </c>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29" t="inlineStr">
+        <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L18" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 06:40:17</t>
-        </is>
-      </c>
-      <c r="N17" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9800 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B18" s="26">
-        <v>10010</v>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erick Mpho Molefe</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–15:00 wharehouse</t>
-        </is>
-      </c>
-      <c r="F18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Erick Mpho Molefe worked 07:00–16:00 on 2026-09-24 (Heritage Day) at wharehouse (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="H18" s="26"/>
-      <c r="I18" s="27">
-        <v>8</v>
-      </c>
-      <c r="J18" s="27">
-        <v>7.5</v>
-      </c>
-      <c r="K18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve adjusted</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:29:03</t>
-        </is>
-      </c>
-      <c r="N18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
+      <c r="M18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 08:58:26</t>
+        </is>
+      </c>
+      <c r="N18" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Event/Venue rate chosen — shift #9789 R934,38 → R640,00 (Venue/event: 12 h × R95 → DIFFERENCE ONLY: Paid last week 08:00–16:00 House/Garden 8.00 h × R62,50 = R500,00 (shift #9705, payroll earlier); 06:00–18:00 at a venue = R1 140,00 (R95,00/h); less the House/Garden already paid R500,00; TO PAY THIS WEEK R640,00)</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11371,7 @@
         </is>
       </c>
       <c r="B19" s="29">
-        <v>10073</v>
+        <v>10140</v>
       </c>
       <c r="C19" s="29" t="inlineStr">
         <is>
@@ -11374,29 +11380,31 @@
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:00–18:00 Warehouse</t>
+          <t xml:space="preserve">08:00–15:00 Garden</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse claimed — but area says “Pretoria and fnb”</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — Givemore — approved R1 000,00 — CHECK HOURS NEXT WEEK</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAREHOUSE CLAIMED BUT AREA SAYS “Pretoria and fnb”: Givemore Chifetete Kuziwa selected Warehouse Team at “Warehouse” for 12.00 h on Thu 17 Sep 2026, but wrote the area as “Pretoria and fnb” — that is a venue, not the warehouse. Other workers were at Botanical garden Pretoria that day. If he was at “Pretoria and fnb”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day: Givemore (gardener) claimed 08:00–16:00. Owner: double the day = R1 000. VERIFY NEXT WEEK whether he actually worked 8 h or 4 h.</t>
         </is>
       </c>
       <c r="H19" s="29"/>
       <c r="I19" s="30">
-        <v>12</v>
-      </c>
-      <c r="J19" s="29"/>
+        <v>7</v>
+      </c>
+      <c r="J19" s="30">
+        <v>7</v>
+      </c>
       <c r="K19" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
@@ -11409,74 +11417,72 @@
       </c>
       <c r="M19" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:58:26</t>
+          <t xml:space="preserve">2026-09-23 10:31:30</t>
         </is>
       </c>
       <c r="N19" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Event/Venue rate chosen — shift #9789 R934,38 → R640,00 (Venue/event: 12 h × R95 → DIFFERENCE ONLY: Paid last week 08:00–16:00 House/Garden 8.00 h × R62,50 = R500,00 (shift #9705, payroll earlier); 06:00–18:00 at a venue = R1 140,00 (R95,00/h); less the House/Garden already paid R500,00; TO PAY THIS WEEK R640,00)</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — gardener, hours set to 08:00–15:00: 7 h × R62,50 × 2 = R875,00. CHECK NEXT WEEK what time he really worked until.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B20" s="29">
-        <v>10140</v>
-      </c>
-      <c r="C20" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Givemore Chifetete Kuziwa</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E20" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08:00–15:00 Garden</t>
-        </is>
-      </c>
-      <c r="F20" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — Givemore — approved R1 000,00 — CHECK HOURS NEXT WEEK</t>
-        </is>
-      </c>
-      <c r="G20" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day: Givemore (gardener) claimed 08:00–16:00. Owner: double the day = R1 000. VERIFY NEXT WEEK whether he actually worked 8 h or 4 h.</t>
-        </is>
-      </c>
-      <c r="H20" s="29"/>
-      <c r="I20" s="30">
-        <v>7</v>
-      </c>
-      <c r="J20" s="30">
-        <v>7</v>
-      </c>
-      <c r="K20" s="29" t="inlineStr">
+      <c r="B20" s="32">
+        <v>10104</v>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac Mbele</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33">
+        <v>9</v>
+      </c>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L20" s="29" t="inlineStr">
+      <c r="L20" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M20" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:31:30</t>
-        </is>
-      </c>
-      <c r="N20" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — gardener, hours set to 08:00–15:00: 7 h × R62,50 × 2 = R875,00. CHECK NEXT WEEK what time he really worked until.</t>
+      <c r="M20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 08:43:25</t>
+        </is>
+      </c>
+      <c r="N20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9850 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11493,7 @@
         </is>
       </c>
       <c r="B21" s="32">
-        <v>10104</v>
+        <v>10106</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -11496,7 +11502,7 @@
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -11531,12 +11537,12 @@
       </c>
       <c r="M21" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:43:25</t>
+          <t xml:space="preserve">2026-09-23 08:43:27</t>
         </is>
       </c>
       <c r="N21" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9850 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9851 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11553,7 @@
         </is>
       </c>
       <c r="B22" s="32">
-        <v>10106</v>
+        <v>10118</v>
       </c>
       <c r="C22" s="32" t="inlineStr">
         <is>
@@ -11556,7 +11562,7 @@
       </c>
       <c r="D22" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="E22" s="32" t="inlineStr">
@@ -11591,12 +11597,12 @@
       </c>
       <c r="M22" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:43:27</t>
+          <t xml:space="preserve">2026-09-23 08:43:31</t>
         </is>
       </c>
       <c r="N22" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9851 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9854 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -11607,7 +11613,7 @@
         </is>
       </c>
       <c r="B23" s="32">
-        <v>10118</v>
+        <v>10125</v>
       </c>
       <c r="C23" s="32" t="inlineStr">
         <is>
@@ -11616,12 +11622,12 @@
       </c>
       <c r="D23" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
@@ -11636,7 +11642,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23" s="32"/>
       <c r="K23" s="32" t="inlineStr">
@@ -11651,12 +11657,12 @@
       </c>
       <c r="M23" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:43:31</t>
+          <t xml:space="preserve">2026-09-23 08:43:34</t>
         </is>
       </c>
       <c r="N23" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9854 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9856 R1 620,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50; R0 until approved)</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11673,7 @@
         </is>
       </c>
       <c r="B24" s="32">
-        <v>10125</v>
+        <v>10141</v>
       </c>
       <c r="C24" s="32" t="inlineStr">
         <is>
@@ -11686,22 +11692,24 @@
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G24" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Isaac Mbele worked 07:00–15:00. Held for owner approval.</t>
         </is>
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="33">
         <v>8</v>
       </c>
-      <c r="J24" s="32"/>
+      <c r="J24" s="33">
+        <v>7.5</v>
+      </c>
       <c r="K24" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve original</t>
+          <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
       <c r="L24" s="32" t="inlineStr">
@@ -11711,12 +11719,12 @@
       </c>
       <c r="M24" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:43:34</t>
+          <t xml:space="preserve">2026-09-23 10:32:01</t>
         </is>
       </c>
       <c r="N24" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9856 R1 620,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50; R0 until approved)</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11735,7 @@
         </is>
       </c>
       <c r="B25" s="32">
-        <v>10141</v>
+        <v>10129</v>
       </c>
       <c r="C25" s="32" t="inlineStr">
         <is>
@@ -11736,34 +11744,32 @@
       </c>
       <c r="D25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–15:00 Warehouse</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Isaac Mbele worked 07:00–15:00. Held for owner approval.</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="33">
-        <v>8</v>
-      </c>
-      <c r="J25" s="33">
-        <v>7.5</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J25" s="32"/>
       <c r="K25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve adjusted</t>
+          <t xml:space="preserve">approve original</t>
         </is>
       </c>
       <c r="L25" s="32" t="inlineStr">
@@ -11773,72 +11779,74 @@
       </c>
       <c r="M25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 10:32:01</t>
+          <t xml:space="preserve">2026-09-23 08:43:37</t>
         </is>
       </c>
       <c r="N25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9858 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B26" s="32">
-        <v>10129</v>
-      </c>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Isaac Mbele</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-25</t>
-        </is>
-      </c>
-      <c r="E26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
-        </is>
-      </c>
-      <c r="G26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
-        </is>
-      </c>
-      <c r="H26" s="32"/>
-      <c r="I26" s="33">
+      <c r="B26" s="17">
+        <v>10122</v>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">John Simbarashe Mhlanga</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-16</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–16:00 Botanical gardens event day</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual overlap review</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-16 for 07:00-16:00.</t>
+        </is>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="18">
         <v>9</v>
       </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L26" s="32" t="inlineStr">
+      <c r="J26" s="18">
+        <v>0</v>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">already paid r0</t>
+        </is>
+      </c>
+      <c r="L26" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 08:43:37</t>
-        </is>
-      </c>
-      <c r="N26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9858 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 08:53:49</t>
+        </is>
+      </c>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALREADY BILLED Wednesday 2026-09-16 · 07:00–16:00 · 9.00 h Normal · Botanical gardens event day · Running the event at botanical Gardens R750,00 · shift #9766 · PAID in payroll 2026-09-12 → 2026-09-18 (closed)</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11857,7 @@
         </is>
       </c>
       <c r="B27" s="17">
-        <v>10122</v>
+        <v>10132</v>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
@@ -11868,15 +11876,17 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual overlap review</t>
+          <t xml:space="preserve">ALREADY PAID — WRONG RATE</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-16 for 07:00-16:00.</t>
-        </is>
-      </c>
-      <c r="H27" s="17"/>
+          <t xml:space="preserve">John was paid Wed 16 Sep 2026 07:00–16:00 · Botanical gardens event day (Pretoria) · Normal · "Running the event at botanical Gardens" · 9.00 h × R90,00 = R750,00 (payroll 2026-09-12). He now claims 07:00–16:00 · Botanical gardens event day (Pretoria) · Normal · "Running the event at botanical Gardens" · 9.00 h for the same day. Same work type, but the rate paid (R90,00/h) differs from the rule (R95,00/h). • Rate correction on the paid hours 07:00–16:00: 9.00 h — worth R855,00 at the correct rule, R750,00 was paid → +R105,00 Still due: R105,00 (full day 9.00 h at the correct rule = R855,00 − R750,00 already paid). Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
+        </is>
+      </c>
+      <c r="H27" s="18">
+        <v>0</v>
+      </c>
       <c r="I27" s="18">
         <v>9</v>
       </c>
@@ -11885,7 +11895,7 @@
       </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already paid r0</t>
+          <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
       <c r="L27" s="17" t="inlineStr">
@@ -11895,12 +11905,12 @@
       </c>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:53:49</t>
+          <t xml:space="preserve">2026-09-23 08:56:44</t>
         </is>
       </c>
       <c r="N27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY BILLED Wednesday 2026-09-16 · 07:00–16:00 · 9.00 h Normal · Botanical gardens event day · Running the event at botanical Gardens R750,00 · shift #9766 · PAID in payroll 2026-09-12 → 2026-09-18 (closed)</t>
+          <t xml:space="preserve">Already paid — WRONG RATE — R105,00 still due — approved amount R105,00</t>
         </is>
       </c>
     </row>
@@ -11911,7 +11921,7 @@
         </is>
       </c>
       <c r="B28" s="17">
-        <v>10132</v>
+        <v>9972</v>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
@@ -11920,32 +11930,30 @@
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Botanical gardens event day</t>
+          <t xml:space="preserve">15:00–20:00 Music Bus</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY PAID — WRONG RATE</t>
+          <t xml:space="preserve">Manual overlap review</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">John was paid Wed 16 Sep 2026 07:00–16:00 · Botanical gardens event day (Pretoria) · Normal · "Running the event at botanical Gardens" · 9.00 h × R90,00 = R750,00 (payroll 2026-09-12). He now claims 07:00–16:00 · Botanical gardens event day (Pretoria) · Normal · "Running the event at botanical Gardens" · 9.00 h for the same day. Same work type, but the rate paid (R90,00/h) differs from the rule (R95,00/h). • Rate correction on the paid hours 07:00–16:00: 9.00 h — worth R855,00 at the correct rule, R750,00 was paid → +R105,00 Still due: R105,00 (full day 9.00 h at the correct rule = R855,00 − R750,00 already paid). Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
-        </is>
-      </c>
-      <c r="H28" s="18">
-        <v>0</v>
-      </c>
+          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-17 for 15:00-20:00.</t>
+        </is>
+      </c>
+      <c r="H28" s="17"/>
       <c r="I28" s="18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J28" s="18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
@@ -11959,12 +11967,12 @@
       </c>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:56:44</t>
+          <t xml:space="preserve">2026-09-23 08:56:08</t>
         </is>
       </c>
       <c r="N28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Already paid — WRONG RATE — R105,00 still due — approved amount R105,00</t>
+          <t xml:space="preserve">ALREADY BILLED Thursday 2026-09-17 · 07:00–16:00 · 9.00 h Normal · FNB Stadium · Setting up R750,00 · shift #9767 · PAID in payroll 2026-09-12 → 2026-09-18 (closed)</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11983,7 @@
         </is>
       </c>
       <c r="B29" s="17">
-        <v>9972</v>
+        <v>10069</v>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
@@ -11994,15 +12002,17 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual overlap review</t>
+          <t xml:space="preserve">ALREADY PAID — EXTRA HOURS</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-17 for 15:00-20:00.</t>
-        </is>
-      </c>
-      <c r="H29" s="17"/>
+          <t xml:space="preserve">John was paid Thu 17 Sep 2026 07:00–16:00 · FNB Stadium (Jhb) · Normal · "Setting up" · 9.00 h × R90,00 = R750,00 (payroll 2026-09-12). He now claims 15:00–20:00 · Music Bus (Thembisa) · Music Bus · "Missed shifts from Thursday doing music bus in Thembisa where there was a trade visit" · 5.00 h for the same day. Work type changed: Normal → Music Bus (rate R90,00 → R120,00). • Extra hours 16:00–20:00: 4.00 h → R480,00 Still due: R480,00 (full day 5.00 h at the correct rule = R1 230,00 − R750,00 already paid). Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
+        </is>
+      </c>
+      <c r="H29" s="18">
+        <v>4</v>
+      </c>
       <c r="I29" s="18">
         <v>5</v>
       </c>
@@ -12021,12 +12031,12 @@
       </c>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 08:56:08</t>
+          <t xml:space="preserve">2026-09-23 09:03:50</t>
         </is>
       </c>
       <c r="N29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY BILLED Thursday 2026-09-17 · 07:00–16:00 · 9.00 h Normal · FNB Stadium · Setting up R750,00 · shift #9767 · PAID in payroll 2026-09-12 → 2026-09-18 (closed)</t>
+          <t xml:space="preserve">Already paid — EXTRA HOURS — R480,00 still due — approved amount R480,00</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12047,7 @@
         </is>
       </c>
       <c r="B30" s="17">
-        <v>10069</v>
+        <v>10072</v>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
@@ -12046,36 +12056,36 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:00–20:00 Music Bus</t>
+          <t xml:space="preserve">07:00–16:00 FNB Stadium</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY PAID — EXTRA HOURS</t>
+          <t xml:space="preserve">ALREADY PAID — SAME SHIFT AGAIN (duplicate)</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">John was paid Thu 17 Sep 2026 07:00–16:00 · FNB Stadium (Jhb) · Normal · "Setting up" · 9.00 h × R90,00 = R750,00 (payroll 2026-09-12). He now claims 15:00–20:00 · Music Bus (Thembisa) · Music Bus · "Missed shifts from Thursday doing music bus in Thembisa where there was a trade visit" · 5.00 h for the same day. Work type changed: Normal → Music Bus (rate R90,00 → R120,00). • Extra hours 16:00–20:00: 4.00 h → R480,00 Still due: R480,00 (full day 5.00 h at the correct rule = R1 230,00 − R750,00 already paid). Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
+          <t xml:space="preserve">John was paid Mon 21 Sep 2026 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h × R95,00 = R855,00 (payroll 2026-09-19). He now claims 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h for the same day. Every hour of this claim is already paid. Nothing is due: R0,00. Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
         </is>
       </c>
       <c r="H30" s="18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30" s="18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J30" s="18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve adjusted</t>
+          <t xml:space="preserve">already paid r0</t>
         </is>
       </c>
       <c r="L30" s="17" t="inlineStr">
@@ -12085,12 +12095,12 @@
       </c>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:03:50</t>
+          <t xml:space="preserve">2026-09-23 09:01:41</t>
         </is>
       </c>
       <c r="N30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Already paid — EXTRA HOURS — R480,00 still due — approved amount R480,00</t>
+          <t xml:space="preserve">Already paid — SAME SHIFT AGAIN (duplicate) — R0,00 still due — approved amount R0,00</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12111,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <v>9979</v>
+        <v>10126</v>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
@@ -12133,11 +12143,11 @@
         <v>9</v>
       </c>
       <c r="J31" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve adjusted</t>
+          <t xml:space="preserve">already paid r0</t>
         </is>
       </c>
       <c r="L31" s="17" t="inlineStr">
@@ -12147,7 +12157,7 @@
       </c>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:01:06</t>
+          <t xml:space="preserve">2026-09-23 09:06:06</t>
         </is>
       </c>
       <c r="N31" s="17" t="inlineStr">
@@ -12163,7 +12173,7 @@
         </is>
       </c>
       <c r="B32" s="17">
-        <v>10072</v>
+        <v>10131</v>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
@@ -12211,7 +12221,7 @@
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:01:41</t>
+          <t xml:space="preserve">2026-09-23 09:03:55</t>
         </is>
       </c>
       <c r="N32" s="17" t="inlineStr">
@@ -12227,7 +12237,7 @@
         </is>
       </c>
       <c r="B33" s="17">
-        <v>10126</v>
+        <v>9983</v>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
@@ -12236,34 +12246,32 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 FNB Stadium</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual overlap review</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-21 for 07:00-16:00.</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="18">
         <v>9</v>
       </c>
-      <c r="J33" s="18">
-        <v>0</v>
-      </c>
+      <c r="J33" s="17"/>
       <c r="K33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already paid r0</t>
+          <t xml:space="preserve">approve original</t>
         </is>
       </c>
       <c r="L33" s="17" t="inlineStr">
@@ -12273,12 +12281,12 @@
       </c>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:06:06</t>
+          <t xml:space="preserve">2026-09-23 09:02:31</t>
         </is>
       </c>
       <c r="N33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY BILLED Monday 2026-09-21 · 07:00–16:00 · 9.00 h Normal · FNB Stadium · Strike down R855,00 · shift #9857 · in THIS payroll (2026-09-19 → 2026-09-25, not yet paid)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9783 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12297,7 @@
         </is>
       </c>
       <c r="B34" s="17">
-        <v>10131</v>
+        <v>10092</v>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
@@ -12298,36 +12306,32 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 FNB Stadium</t>
+          <t xml:space="preserve">07:00–12:00 Warehouse</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY PAID — SAME SHIFT AGAIN (duplicate)</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">John was paid Mon 21 Sep 2026 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h × R95,00 = R855,00 (payroll 2026-09-19). He now claims 07:00–16:00 · FNB Stadium (Soweto jhb) · Normal · "Strike down" · 9.00 h for the same day. Every hour of this claim is already paid. Nothing is due: R0,00. Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
-        </is>
-      </c>
-      <c r="H34" s="18">
-        <v>0</v>
-      </c>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H34" s="17"/>
       <c r="I34" s="18">
-        <v>9</v>
-      </c>
-      <c r="J34" s="18">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J34" s="17"/>
       <c r="K34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">already paid r0</t>
+          <t xml:space="preserve">approve original</t>
         </is>
       </c>
       <c r="L34" s="17" t="inlineStr">
@@ -12337,12 +12341,12 @@
       </c>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:03:55</t>
+          <t xml:space="preserve">2026-09-23 09:02:56</t>
         </is>
       </c>
       <c r="N34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Already paid — SAME SHIFT AGAIN (duplicate) — R0,00 still due — approved amount R0,00</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9846 R900,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 5 h × R162,50 (R81,25 × 2, no meeting deduction) = R812,50; R0 until approved)</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12357,7 @@
         </is>
       </c>
       <c r="B35" s="17">
-        <v>9983</v>
+        <v>10095</v>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
@@ -12362,32 +12366,34 @@
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">12:00–18:00 Music Bus</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: John Simbarashe Mhlanga worked 12:00–18:00 on 2026-09-24 (Heritage Day) at Music Bus (Music Bus). Public-holiday work is not paid automatically. Recommended: Music Bus public holiday (Heritage Day): R750 fixed 07–16 + 2 h outside 07–16 × R180 = R1 110,00. R0 is paid until the owner approves or declines.</t>
         </is>
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="18">
-        <v>9</v>
-      </c>
-      <c r="J35" s="17"/>
+        <v>6</v>
+      </c>
+      <c r="J35" s="18">
+        <v>6</v>
+      </c>
       <c r="K35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve original</t>
+          <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
       <c r="L35" s="17" t="inlineStr">
@@ -12397,12 +12403,12 @@
       </c>
       <c r="M35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:02:31</t>
+          <t xml:space="preserve">2026-09-23 09:05:05</t>
         </is>
       </c>
       <c r="N35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9783 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved — R1 110,00 (as recommended)</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12419,7 @@
         </is>
       </c>
       <c r="B36" s="17">
-        <v>10092</v>
+        <v>10144</v>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
@@ -12432,19 +12438,21 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): John Simbarashe Mhlanga worked 07:00–12:00. Held for owner approval.</t>
         </is>
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="18">
         <v>5</v>
       </c>
-      <c r="J36" s="17"/>
+      <c r="J36" s="18">
+        <v>4.5</v>
+      </c>
       <c r="K36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
@@ -12457,12 +12465,12 @@
       </c>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:02:56</t>
+          <t xml:space="preserve">2026-09-23 10:31:24</t>
         </is>
       </c>
       <c r="N36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9846 R900,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 5 h × R162,50 (R81,25 × 2, no meeting deduction) = R812,50; R0 until approved)</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day): 5 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 4.5 h × R162,50 (R81,25 × 2) = R731,25</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12481,7 @@
         </is>
       </c>
       <c r="B37" s="17">
-        <v>10095</v>
+        <v>10098</v>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
@@ -12482,171 +12490,173 @@
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:00–18:00 Music Bus</t>
+          <t xml:space="preserve">07:00–11:00 Warehouse</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: John Simbarashe Mhlanga worked 12:00–18:00 on 2026-09-24 (Heritage Day) at Music Bus (Music Bus). Public-holiday work is not paid automatically. Recommended: Music Bus public holiday (Heritage Day): R750 fixed 07–16 + 2 h outside 07–16 × R180 = R1 110,00. R0 is paid until the owner approves or declines.</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="18">
+        <v>4</v>
+      </c>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 09:03:07</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9848 R750,00 → R284,38 (Warehouse: 4 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 3.5 h × R81,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B38" s="20">
+        <v>10109</v>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joshua Motsamai Nteo</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-13</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–13:00 Pastdal pretoria</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual overlap review</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-13 for 07:00-13:00.</t>
+        </is>
+      </c>
+      <c r="H38" s="20"/>
+      <c r="I38" s="21">
         <v>6</v>
       </c>
-      <c r="J37" s="18">
+      <c r="J38" s="21">
+        <v>0</v>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">already paid r0</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 09:08:42</t>
+        </is>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALREADY BILLED Sunday 2026-09-13 · 07:00–13:00 · 6.00 h Normal · Pastdal pub · Strikedown R720,00 · shift #9638 · PAID in payroll 2026-09-12 → 2026-09-18 (closed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B39" s="20">
+        <v>10113</v>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joshua Motsamai Nteo</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-13</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–13:00 Pastdal pretoria</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALREADY PAID — this claim is covered by what was paid</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joshua was paid Sun 13 Sep 2026 07:00–13:00 · Pastdal pub (Pretoria) · Normal · "Strikedown" · 6.00 h × R120,00 = R720,00 (payroll 2026-09-12). He now claims 07:00–13:00 · Pastdal pretoria (Pretoria) · Normal · "Break down" · 6.00 h for the same day. Same work type, but the rate paid (R120,00/h) differs from the rule (R114,00/h). • Rate correction on the paid hours 07:00–13:00: 6.00 h — worth R684,00 at the correct rule, R720,00 was paid → −R36,00 What was paid (R720,00) already covers this claim (R684,00 at the correct rule). Nothing more is due: R0,00. Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
+        </is>
+      </c>
+      <c r="H39" s="21">
+        <v>0</v>
+      </c>
+      <c r="I39" s="21">
         <v>6</v>
       </c>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve adjusted</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
+      <c r="J39" s="21">
+        <v>0</v>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">already paid r0</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 09:05:05</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved — R1 110,00 (as recommended)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B38" s="17">
-        <v>10144</v>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">John Simbarashe Mhlanga</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–12:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): John Simbarashe Mhlanga worked 07:00–12:00. Held for owner approval.</t>
-        </is>
-      </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18">
-        <v>5</v>
-      </c>
-      <c r="J38" s="18">
-        <v>4.5</v>
-      </c>
-      <c r="K38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:31:24</t>
-        </is>
-      </c>
-      <c r="N38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day): 5 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 4.5 h × R162,50 (R81,25 × 2) = R731,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B39" s="17">
-        <v>10098</v>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">John Simbarashe Mhlanga</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-25</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–11:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
-        </is>
-      </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="18">
-        <v>4</v>
-      </c>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 09:03:07</t>
-        </is>
-      </c>
-      <c r="N39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9848 R750,00 → R284,38 (Warehouse: 4 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 3.5 h × R81,25)</t>
+      <c r="M39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 09:21:54</t>
+        </is>
+      </c>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already paid — this claim is covered by what was paid — R0,00 still due — approved amount R0,00</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12667,7 @@
         </is>
       </c>
       <c r="B40" s="20">
-        <v>10109</v>
+        <v>9959</v>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
@@ -12666,34 +12676,32 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–13:00 Pastdal pretoria</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual overlap review</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-13 for 07:00-13:00.</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H40" s="20"/>
       <c r="I40" s="21">
-        <v>6</v>
-      </c>
-      <c r="J40" s="21">
-        <v>0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J40" s="20"/>
       <c r="K40" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">already paid r0</t>
+          <t xml:space="preserve">approve original</t>
         </is>
       </c>
       <c r="L40" s="20" t="inlineStr">
@@ -12703,12 +12711,12 @@
       </c>
       <c r="M40" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:08:42</t>
+          <t xml:space="preserve">2026-09-23 09:09:09</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY BILLED Sunday 2026-09-13 · 07:00–13:00 · 6.00 h Normal · Pastdal pub · Strikedown R720,00 · shift #9638 · PAID in payroll 2026-09-12 → 2026-09-18 (closed)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9774 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12727,7 @@
         </is>
       </c>
       <c r="B41" s="20">
-        <v>10113</v>
+        <v>9964</v>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
@@ -12728,36 +12736,32 @@
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–13:00 Pastdal pretoria</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALREADY PAID — this claim is covered by what was paid</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joshua was paid Sun 13 Sep 2026 07:00–13:00 · Pastdal pub (Pretoria) · Normal · "Strikedown" · 6.00 h × R120,00 = R720,00 (payroll 2026-09-12). He now claims 07:00–13:00 · Pastdal pretoria (Pretoria) · Normal · "Break down" · 6.00 h for the same day. Same work type, but the rate paid (R120,00/h) differs from the rule (R114,00/h). • Rate correction on the paid hours 07:00–13:00: 6.00 h — worth R684,00 at the correct rule, R720,00 was paid → −R36,00 What was paid (R720,00) already covers this claim (R684,00 at the correct rule). Nothing more is due: R0,00. Hours from Wednesday onwards are estimated for the auditor run; this entry corrects them. Bernie to approve — nothing has been changed.</t>
-        </is>
-      </c>
-      <c r="H41" s="21">
-        <v>0</v>
-      </c>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H41" s="20"/>
       <c r="I41" s="21">
-        <v>6</v>
-      </c>
-      <c r="J41" s="21">
-        <v>0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J41" s="20"/>
       <c r="K41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">already paid r0</t>
+          <t xml:space="preserve">approve original</t>
         </is>
       </c>
       <c r="L41" s="20" t="inlineStr">
@@ -12767,12 +12771,12 @@
       </c>
       <c r="M41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:21:54</t>
+          <t xml:space="preserve">2026-09-23 09:09:11</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Already paid — this claim is covered by what was paid — R0,00 still due — approved amount R0,00</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9778 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12787,7 @@
         </is>
       </c>
       <c r="B42" s="20">
-        <v>9959</v>
+        <v>10110</v>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
@@ -12792,7 +12796,7 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
@@ -12802,22 +12806,24 @@
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Manual overlap review</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-23 for 07:00-16:00.</t>
         </is>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="21">
         <v>9</v>
       </c>
-      <c r="J42" s="20"/>
+      <c r="J42" s="21">
+        <v>0</v>
+      </c>
       <c r="K42" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve original</t>
+          <t xml:space="preserve">already paid r0</t>
         </is>
       </c>
       <c r="L42" s="20" t="inlineStr">
@@ -12827,12 +12833,12 @@
       </c>
       <c r="M42" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:09:09</t>
+          <t xml:space="preserve">2026-09-23 09:20:39</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9774 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">already billed</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12849,7 @@
         </is>
       </c>
       <c r="B43" s="20">
-        <v>9964</v>
+        <v>10111</v>
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
@@ -12887,12 +12893,12 @@
       </c>
       <c r="M43" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:09:11</t>
+          <t xml:space="preserve">2026-09-23 09:22:36</t>
         </is>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9778 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9853 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -12903,7 +12909,7 @@
         </is>
       </c>
       <c r="B44" s="20">
-        <v>10110</v>
+        <v>9977</v>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
@@ -12912,34 +12918,32 @@
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual overlap review</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G44" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same employee has another overlapping entry on 2026-09-23 for 07:00-16:00.</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H44" s="20"/>
       <c r="I44" s="21">
-        <v>9</v>
-      </c>
-      <c r="J44" s="21">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J44" s="20"/>
       <c r="K44" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">already paid r0</t>
+          <t xml:space="preserve">approve original</t>
         </is>
       </c>
       <c r="L44" s="20" t="inlineStr">
@@ -12949,12 +12953,12 @@
       </c>
       <c r="M44" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:20:39</t>
+          <t xml:space="preserve">2026-09-23 09:21:05</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">already billed</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9780 R1 620,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50; R0 until approved)</t>
         </is>
       </c>
     </row>
@@ -12965,7 +12969,7 @@
         </is>
       </c>
       <c r="B45" s="20">
-        <v>10111</v>
+        <v>10135</v>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
@@ -12974,413 +12978,415 @@
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Joshua Motsamai Nteo worked 07:00–16:00 at Warehouse (Meyerton), Cleaning warehouse. Held for owner approval.</t>
         </is>
       </c>
       <c r="H45" s="20"/>
       <c r="I45" s="21">
+        <v>8</v>
+      </c>
+      <c r="J45" s="21">
+        <v>7.5</v>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve adjusted</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 10:29:15</t>
+        </is>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B46" s="23">
+        <v>9954</v>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrick Ngozo</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–16:00 Wearhouse</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Venue/Event</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The wording says Wearhouse — Loading but the work type is Normal. Choose Warehouse (R81,25/h, 9.5 h less 0.5 h staff meeting = R731,25) or Venue/Event (R95/h = R902,50). The shift stays at R795 until you choose.</t>
+        </is>
+      </c>
+      <c r="H46" s="23"/>
+      <c r="I46" s="24">
+        <v>9.5</v>
+      </c>
+      <c r="J46" s="23"/>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22 12:28:15</t>
+        </is>
+      </c>
+      <c r="N46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9773 R795,00 → R731,25 (Warehouse: 9.5 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 9 h × R81,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B47" s="23">
+        <v>10143</v>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrick Ngozo</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–15:00 Wearhouse</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Patrick Ngozo worked 06:30–15:00. Held for owner approval.</t>
+        </is>
+      </c>
+      <c r="H47" s="23"/>
+      <c r="I47" s="24">
+        <v>8.5</v>
+      </c>
+      <c r="J47" s="24">
+        <v>8</v>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 10:30:29</t>
+        </is>
+      </c>
+      <c r="N47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day), owner set hours 06:30–15:00: 8.5 h − 0.5 h staff meeting = 8 h × R162,50 = R1 300,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B48" s="26">
+        <v>10063</v>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solomon Moyo</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H48" s="26"/>
+      <c r="I48" s="27">
         <v>9</v>
       </c>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20" t="inlineStr">
+      <c r="J48" s="26"/>
+      <c r="K48" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L45" s="20" t="inlineStr">
+      <c r="L48" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M45" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 09:22:36</t>
-        </is>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9853 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="M48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 10:48:16</t>
+        </is>
+      </c>
+      <c r="N48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9835 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B46" s="20">
-        <v>9977</v>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joshua Motsamai Nteo</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="B49" s="26">
+        <v>10060</v>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solomon Moyo</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
-      <c r="F46" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
-        </is>
-      </c>
-      <c r="H46" s="20"/>
-      <c r="I46" s="21">
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Solomon Moyo worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Botanical Gardens (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
+        </is>
+      </c>
+      <c r="H49" s="26"/>
+      <c r="I49" s="27">
         <v>8</v>
       </c>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20" t="inlineStr">
+      <c r="J49" s="27">
+        <v>7.5</v>
+      </c>
+      <c r="K49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve adjusted</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 10:31:21</t>
+        </is>
+      </c>
+      <c r="N49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — warehouse, hours set to 07:00–15:00 (worker wrote Botanical Gardens until 16:00): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1 218,75</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B50" s="29">
+        <v>10074</v>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="E50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–18:00 FNB</t>
+        </is>
+      </c>
+      <c r="F50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse claimed — but the entry names “Johannesburg”</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAREHOUSE CLAIMED BUT THE ENTRY NAMES “Johannesburg”: Takavaudza Chokuda selected Warehouse Team at “FNB” for 2.00 h on Thu 17 Sep 2026, but wrote “Johannesburg” — that is a venue, not the warehouse. 6 workers were at a venue that day (Additional 5 hour shift - 17/09/2026 Parys Golf Day, Botanical garden Pretoria, FNB Stadium, Parys golf &amp; country Estate, Parys Country Club, Parys, Botanical gardens, Fnb stadium). If he was at “Johannesburg”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+        </is>
+      </c>
+      <c r="H50" s="29"/>
+      <c r="I50" s="30">
+        <v>2</v>
+      </c>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L46" s="20" t="inlineStr">
+      <c r="L50" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M46" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 09:21:05</t>
-        </is>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9780 R1 620,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50; R0 until approved)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="M50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 11:01:57</t>
+        </is>
+      </c>
+      <c r="N50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Event/Venue rate chosen — shift #9815 R162,50 → R190,00 (Venue/event: 2 h × R95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B47" s="20">
-        <v>10135</v>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joshua Motsamai Nteo</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–15:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Joshua Motsamai Nteo worked 07:00–16:00 at Warehouse (Meyerton), Cleaning warehouse. Held for owner approval.</t>
-        </is>
-      </c>
-      <c r="H47" s="20"/>
-      <c r="I47" s="21">
-        <v>8</v>
-      </c>
-      <c r="J47" s="21">
-        <v>7.5</v>
-      </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve adjusted</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
+      <c r="B51" s="29">
+        <v>9955</v>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+        </is>
+      </c>
+      <c r="F51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crew pattern — 8 of 9 at a venue, this one says Warehouse</t>
+        </is>
+      </c>
+      <c r="G51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CREW PATTERN: 8 of 9 workers were at a venue on Mon 21 Sep 2026 (FNB Stadium, FNB strike down, Fnb stadium) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
+        </is>
+      </c>
+      <c r="H51" s="29"/>
+      <c r="I51" s="30">
+        <v>9</v>
+      </c>
+      <c r="J51" s="30">
+        <v>9</v>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L51" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:29:15</t>
-        </is>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B48" s="23">
-        <v>9954</v>
-      </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-22</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06:30–16:00 Wearhouse</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Venue/Event</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The wording says Wearhouse — Loading but the work type is Normal. Choose Warehouse (R81,25/h, 9.5 h less 0.5 h staff meeting = R731,25) or Venue/Event (R95/h = R902,50). The shift stays at R795 until you choose.</t>
-        </is>
-      </c>
-      <c r="H48" s="23"/>
-      <c r="I48" s="24">
-        <v>9.5</v>
-      </c>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-22 12:28:15</t>
-        </is>
-      </c>
-      <c r="N48" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9773 R795,00 → R731,25 (Warehouse: 9.5 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 9 h × R81,25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B49" s="23">
-        <v>10143</v>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
-        </is>
-      </c>
-      <c r="D49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06:30–15:00 Wearhouse</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Patrick Ngozo worked 06:30–15:00. Held for owner approval.</t>
-        </is>
-      </c>
-      <c r="H49" s="23"/>
-      <c r="I49" s="24">
-        <v>8.5</v>
-      </c>
-      <c r="J49" s="24">
-        <v>8</v>
-      </c>
-      <c r="K49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:30:29</t>
-        </is>
-      </c>
-      <c r="N49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day), owner set hours 06:30–15:00: 8.5 h − 0.5 h staff meeting = 8 h × R162,50 = R1 300,00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B50" s="26">
-        <v>10063</v>
-      </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solomon Moyo</t>
-        </is>
-      </c>
-      <c r="D50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-22</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
-        </is>
-      </c>
-      <c r="G50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
-        </is>
-      </c>
-      <c r="H50" s="26"/>
-      <c r="I50" s="27">
-        <v>9</v>
-      </c>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:48:16</t>
-        </is>
-      </c>
-      <c r="N50" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9835 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B51" s="26">
-        <v>10060</v>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solomon Moyo</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–15:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Solomon Moyo worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Botanical Gardens (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="H51" s="26"/>
-      <c r="I51" s="27">
-        <v>8</v>
-      </c>
-      <c r="J51" s="27">
-        <v>7.5</v>
-      </c>
-      <c r="K51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve adjusted</t>
-        </is>
-      </c>
-      <c r="L51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:31:21</t>
-        </is>
-      </c>
-      <c r="N51" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — warehouse, hours set to 07:00–15:00 (worker wrote Botanical Gardens until 16:00): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1 218,75</t>
+      <c r="M51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 11:01:58</t>
+        </is>
+      </c>
+      <c r="N51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAREHOUSE — R81,25/h chosen by Bernie Burness for draft #830 — will pay R690,63 when final-submitted (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13397,7 @@
         </is>
       </c>
       <c r="B52" s="29">
-        <v>10074</v>
+        <v>10075</v>
       </c>
       <c r="C52" s="29" t="inlineStr">
         <is>
@@ -13400,27 +13406,27 @@
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00–18:00 FNB</t>
+          <t xml:space="preserve">07:00–16:00 Riverside</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse claimed — but the entry names “Johannesburg”</t>
+          <t xml:space="preserve">Warehouse claimed — but the entry names “The vaal”</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAREHOUSE CLAIMED BUT THE ENTRY NAMES “Johannesburg”: Takavaudza Chokuda selected Warehouse Team at “FNB” for 2.00 h on Thu 17 Sep 2026, but wrote “Johannesburg” — that is a venue, not the warehouse. 6 workers were at a venue that day (Additional 5 hour shift - 17/09/2026 Parys Golf Day, Botanical garden Pretoria, FNB Stadium, Parys golf &amp; country Estate, Parys Country Club, Parys, Botanical gardens, Fnb stadium). If he was at “Johannesburg”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+          <t xml:space="preserve">WAREHOUSE CLAIMED BUT THE ENTRY NAMES “The vaal”: Takavaudza Chokuda selected Warehouse Team at “Riverside” for 9.00 h on Wed 23 Sep 2026, but wrote “The vaal” — that is a venue, not the warehouse. 6 workers were at a venue that day (Work with the Team, wharehouse, Set up vaal Boating, Riverside sun, Vaal Boating Season, Stone Haven And Riverside Sun). If he was at “The vaal”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
         </is>
       </c>
       <c r="H52" s="29"/>
       <c r="I52" s="30">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J52" s="29"/>
       <c r="K52" s="29" t="inlineStr">
@@ -13440,7 +13446,7 @@
       </c>
       <c r="N52" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Event/Venue rate chosen — shift #9815 R162,50 → R190,00 (Venue/event: 2 h × R95)</t>
+          <t xml:space="preserve">Event/Venue rate chosen — shift #9819 R690,63 → R855,00 (Venue/event: 9 h × R95)</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13457,7 @@
         </is>
       </c>
       <c r="B53" s="29">
-        <v>9955</v>
+        <v>10039</v>
       </c>
       <c r="C53" s="29" t="inlineStr">
         <is>
@@ -13460,34 +13466,34 @@
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crew pattern — 8 of 9 at a venue, this one says Warehouse</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G53" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREW PATTERN: 8 of 9 workers were at a venue on Mon 21 Sep 2026 (FNB Stadium, FNB strike down, Fnb stadium) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Takavaudza Chokuda worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Warehouse Team). Public-holiday work is not paid automatically. Recommended: Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50. R0 is paid until the owner approves or declines.</t>
         </is>
       </c>
       <c r="H53" s="29"/>
       <c r="I53" s="30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J53" s="30">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="K53" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve original</t>
+          <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
       <c r="L53" s="29" t="inlineStr">
@@ -13497,12 +13503,12 @@
       </c>
       <c r="M53" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 11:01:58</t>
+          <t xml:space="preserve">2026-09-23 10:32:07</t>
         </is>
       </c>
       <c r="N53" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAREHOUSE — R81,25/h chosen by Bernie Burness for draft #830 — will pay R690,63 when final-submitted (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13519,7 @@
         </is>
       </c>
       <c r="B54" s="29">
-        <v>10075</v>
+        <v>10076</v>
       </c>
       <c r="C54" s="29" t="inlineStr">
         <is>
@@ -13522,22 +13528,22 @@
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Riverside</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse claimed — but the entry names “The vaal”</t>
+          <t xml:space="preserve">Crew pattern — 7 of 8 at a venue, this one says Warehouse</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAREHOUSE CLAIMED BUT THE ENTRY NAMES “The vaal”: Takavaudza Chokuda selected Warehouse Team at “Riverside” for 9.00 h on Wed 23 Sep 2026, but wrote “The vaal” — that is a venue, not the warehouse. 6 workers were at a venue that day (Work with the Team, wharehouse, Set up vaal Boating, Riverside sun, Vaal Boating Season, Stone Haven And Riverside Sun). If he was at “The vaal”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+          <t xml:space="preserve">CREW PATTERN: 7 of 8 workers were at a venue on Fri 25 Sep 2026 (The Capital Sandton and Bonitical Emmarentia, Pretoria country club, Botanical, Vaal Boating, Riverside sun, Pretoria Country Club, Capital hotel / botanical gardens JHB) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
         </is>
       </c>
       <c r="H54" s="29"/>
@@ -13557,134 +13563,132 @@
       </c>
       <c r="M54" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 11:01:57</t>
+          <t xml:space="preserve">2026-09-23 11:01:58</t>
         </is>
       </c>
       <c r="N54" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Event/Venue rate chosen — shift #9819 R690,63 → R855,00 (Venue/event: 9 h × R95)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9817 R690,63 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B55" s="29">
-        <v>10039</v>
-      </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
-        </is>
-      </c>
-      <c r="D55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–15:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Takavaudza Chokuda worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Warehouse Team). Public-holiday work is not paid automatically. Recommended: Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="H55" s="29"/>
-      <c r="I55" s="30">
-        <v>8</v>
-      </c>
-      <c r="J55" s="30">
-        <v>7.5</v>
-      </c>
-      <c r="K55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve adjusted</t>
-        </is>
-      </c>
-      <c r="L55" s="29" t="inlineStr">
+      <c r="B55" s="32">
+        <v>10080</v>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thandanani Nkala</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="E55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–16:00 FNB Stadium and Warehouse</t>
+        </is>
+      </c>
+      <c r="F55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+        </is>
+      </c>
+      <c r="G55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H55" s="32"/>
+      <c r="I55" s="33">
+        <v>9</v>
+      </c>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L55" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:32:07</t>
-        </is>
-      </c>
-      <c r="N55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
+      <c r="M55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 09:24:21</t>
+        </is>
+      </c>
+      <c r="N55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Event/Venue rate chosen — shift #9840 R750,00 → R855,00 (Venue/event: 9 h × R95)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B56" s="29">
-        <v>10076</v>
-      </c>
-      <c r="C56" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
-        </is>
-      </c>
-      <c r="D56" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-25</t>
-        </is>
-      </c>
-      <c r="E56" s="29" t="inlineStr">
+      <c r="B56" s="32">
+        <v>10087</v>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thandanani Nkala</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="E56" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
-      <c r="F56" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crew pattern — 7 of 8 at a venue, this one says Warehouse</t>
-        </is>
-      </c>
-      <c r="G56" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CREW PATTERN: 7 of 8 workers were at a venue on Fri 25 Sep 2026 (The Capital Sandton and Bonitical Emmarentia, Pretoria country club, Botanical, Vaal Boating, Riverside sun, Pretoria Country Club, Capital hotel / botanical gardens JHB) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
-        </is>
-      </c>
-      <c r="H56" s="29"/>
-      <c r="I56" s="30">
+      <c r="F56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+        </is>
+      </c>
+      <c r="G56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H56" s="32"/>
+      <c r="I56" s="33">
         <v>9</v>
       </c>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29" t="inlineStr">
+      <c r="J56" s="32"/>
+      <c r="K56" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L56" s="29" t="inlineStr">
+      <c r="L56" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M56" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 11:01:58</t>
-        </is>
-      </c>
-      <c r="N56" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9817 R690,63 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+      <c r="M56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 09:24:24</t>
+        </is>
+      </c>
+      <c r="N56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9844 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13699,7 @@
         </is>
       </c>
       <c r="B57" s="32">
-        <v>10080</v>
+        <v>10084</v>
       </c>
       <c r="C57" s="32" t="inlineStr">
         <is>
@@ -13704,12 +13708,12 @@
       </c>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 FNB Stadium and Warehouse</t>
+          <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
       <c r="F57" s="32" t="inlineStr">
@@ -13724,7 +13728,7 @@
       </c>
       <c r="H57" s="32"/>
       <c r="I57" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J57" s="32"/>
       <c r="K57" s="32" t="inlineStr">
@@ -13739,12 +13743,12 @@
       </c>
       <c r="M57" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:24:21</t>
+          <t xml:space="preserve">2026-09-23 09:24:33</t>
         </is>
       </c>
       <c r="N57" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Event/Venue rate chosen — shift #9840 R750,00 → R855,00 (Venue/event: 9 h × R95)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9842 R1 620,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50; R0 until approved)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13759,7 @@
         </is>
       </c>
       <c r="B58" s="32">
-        <v>10087</v>
+        <v>10142</v>
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
@@ -13764,32 +13768,34 @@
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Thandanani Nkala worked 07:00–15:00. Held for owner approval.</t>
         </is>
       </c>
       <c r="H58" s="32"/>
       <c r="I58" s="33">
-        <v>9</v>
-      </c>
-      <c r="J58" s="32"/>
+        <v>8</v>
+      </c>
+      <c r="J58" s="33">
+        <v>7.5</v>
+      </c>
       <c r="K58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">approve original</t>
+          <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
       <c r="L58" s="32" t="inlineStr">
@@ -13799,12 +13805,12 @@
       </c>
       <c r="M58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:24:24</t>
+          <t xml:space="preserve">2026-09-23 10:32:12</t>
         </is>
       </c>
       <c r="N58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9844 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13821,7 @@
         </is>
       </c>
       <c r="B59" s="32">
-        <v>10084</v>
+        <v>10082</v>
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
@@ -13824,12 +13830,12 @@
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–15:00 Warehouse</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -13844,7 +13850,7 @@
       </c>
       <c r="H59" s="32"/>
       <c r="I59" s="33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J59" s="32"/>
       <c r="K59" s="32" t="inlineStr">
@@ -13859,194 +13865,72 @@
       </c>
       <c r="M59" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 09:24:33</t>
+          <t xml:space="preserve">2026-09-23 09:24:36</t>
         </is>
       </c>
       <c r="N59" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9842 R1 620,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50; R0 until approved)</t>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9841 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="inlineStr">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B60" s="32">
-        <v>10142</v>
-      </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
-        </is>
-      </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="B60" s="17">
+        <v>10033</v>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
-      <c r="E60" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–15:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F60" s="32" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–14:00 Warehouse</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
-      <c r="G60" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Thandanani Nkala worked 07:00–15:00. Held for owner approval.</t>
-        </is>
-      </c>
-      <c r="H60" s="32"/>
-      <c r="I60" s="33">
-        <v>8</v>
-      </c>
-      <c r="J60" s="33">
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Tsotlego Petrus Malakoane worked 06:30–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Normal). Public-holiday work is not paid automatically. Recommended: Petrus public holiday (Heritage Day): no fixed day — 9.5 h × R160 (R80 × 2) = R1 520,00. R0 is paid until the owner approves or declines.</t>
+        </is>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="18">
         <v>7.5</v>
       </c>
-      <c r="K60" s="32" t="inlineStr">
+      <c r="J60" s="18">
+        <v>7</v>
+      </c>
+      <c r="K60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
-      <c r="L60" s="32" t="inlineStr">
+      <c r="L60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M60" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:32:12</t>
-        </is>
-      </c>
-      <c r="N60" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B61" s="32">
-        <v>10082</v>
-      </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
-        </is>
-      </c>
-      <c r="D61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-25</t>
-        </is>
-      </c>
-      <c r="E61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
-        </is>
-      </c>
-      <c r="G61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
-        </is>
-      </c>
-      <c r="H61" s="32"/>
-      <c r="I61" s="33">
-        <v>9</v>
-      </c>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 09:24:36</t>
-        </is>
-      </c>
-      <c r="N61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9841 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B62" s="17">
-        <v>10033</v>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06:30–14:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Tsotlego Petrus Malakoane worked 06:30–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Normal). Public-holiday work is not paid automatically. Recommended: Petrus public holiday (Heritage Day): no fixed day — 9.5 h × R160 (R80 × 2) = R1 520,00. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="H62" s="17"/>
-      <c r="I62" s="18">
-        <v>7.5</v>
-      </c>
-      <c r="J62" s="18">
-        <v>7</v>
-      </c>
-      <c r="K62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve adjusted</t>
-        </is>
-      </c>
-      <c r="L62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M62" s="17" t="inlineStr">
+      <c r="M60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 11:02:04</t>
         </is>
       </c>
-      <c r="N62" s="17" t="inlineStr">
+      <c r="N60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 06:30–14:00, meeting deducted: 7 h × R160 = R1 120,00. Owner not 100% sure of the end time — CONFIRM NEXT WEEK.</t>
         </is>
@@ -14378,43 +14262,43 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2</t>
+          <t xml:space="preserve">#7</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac Mbele</t>
+          <t xml:space="preserve">Erick Mpho Molefe</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 August Morning mother this week I spent joo aim loan 300 hundred ple</t>
+          <t xml:space="preserve">22 Sep 2026 WhatsApp 07:15: "Goodmorning Mama, can I please have R600 </t>
         </is>
       </c>
       <c r="F13" s="4">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="G13" s="4">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H13" s="4">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J13" s="4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
@@ -14430,7 +14314,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3</t>
+          <t xml:space="preserve">#2</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
@@ -14440,33 +14324,33 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-17</t>
+          <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morning mother joo aim asking 600 hundred loan please</t>
+          <t xml:space="preserve">3 August Morning mother this week I spent joo aim loan 300 hundred ple</t>
         </is>
       </c>
       <c r="F14" s="4">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G14" s="4">
         <v>250</v>
       </c>
       <c r="H14" s="4">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="I14" s="5">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="J14" s="4">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
@@ -14482,7 +14366,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#6</t>
+          <t xml:space="preserve">#3</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -14492,175 +14376,201 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morning mother my kids are having a trip off 1500 but aim short of 600</t>
+          <t xml:space="preserve">Morning mother joo aim asking 600 hundred loan please</t>
         </is>
       </c>
       <c r="F15" s="4">
         <v>600</v>
       </c>
       <c r="G15" s="4">
+        <v>250</v>
+      </c>
+      <c r="H15" s="4">
+        <v>450</v>
+      </c>
+      <c r="I15" s="5">
+        <v>150</v>
+      </c>
+      <c r="J15" s="4">
+        <v>150</v>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weekly</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#6</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac Mbele</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-01</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-02</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning mother my kids are having a trip off 1500 but aim short of 600</t>
+        </is>
+      </c>
+      <c r="F16" s="4">
         <v>600</v>
       </c>
-      <c r="H15" s="4">
+      <c r="G16" s="4">
+        <v>600</v>
+      </c>
+      <c r="H16" s="4">
         <v>0</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I16" s="5">
         <v>600</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J16" s="4">
         <v>600</v>
       </c>
-      <c r="K15" s="0" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">weekly</t>
         </is>
       </c>
-      <c r="L15" s="0" t="inlineStr">
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">active</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#8</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac Mbele</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-26</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 Sep 2026 WhatsApp 08:15: "Mother so like. Aim not well balanced abo</t>
+        </is>
+      </c>
+      <c r="F17" s="4">
+        <v>500</v>
+      </c>
+      <c r="G17" s="4">
+        <v>250</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>500</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weekly</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">LOAN REPAYMENT HISTORY (all payrolls)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Loan #</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Employee</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Payroll week</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Recorded at</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Result</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Scheduled</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deducted</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Balance before</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Balance after</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#1</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erick Mpho Molefe</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
-        </is>
-      </c>
-      <c r="D19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-11 10:12</t>
-        </is>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deducted</t>
-        </is>
-      </c>
-      <c r="F19" s="4">
-        <v>500</v>
-      </c>
-      <c r="G19" s="4">
-        <v>500</v>
-      </c>
-      <c r="H19" s="4">
-        <v>2000</v>
-      </c>
-      <c r="I19" s="4">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#1</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erick Mpho Molefe</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
-        </is>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
-        </is>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deducted</t>
-        </is>
-      </c>
-      <c r="F20" s="4">
-        <v>500</v>
-      </c>
-      <c r="G20" s="4">
-        <v>500</v>
-      </c>
-      <c r="H20" s="4">
-        <v>1500</v>
-      </c>
-      <c r="I20" s="4">
-        <v>1000</v>
       </c>
     </row>
     <row r="21">
@@ -14676,12 +14586,12 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-11 10:12</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
@@ -14696,70 +14606,70 @@
         <v>500</v>
       </c>
       <c r="H21" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I21" s="4">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2</t>
+          <t xml:space="preserve">#1</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac Mbele</t>
+          <t xml:space="preserve">Erick Mpho Molefe</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 09:42</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deferred</t>
+          <t xml:space="preserve">deducted</t>
         </is>
       </c>
       <c r="F22" s="4">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G22" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H22" s="4">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="I22" s="4">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2</t>
+          <t xml:space="preserve">#1</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac Mbele</t>
+          <t xml:space="preserve">Erick Mpho Molefe</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
+          <t xml:space="preserve">2026-09-07 12:01</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
@@ -14768,16 +14678,16 @@
         </is>
       </c>
       <c r="F23" s="4">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G23" s="4">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H23" s="4">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I23" s="4">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24">
@@ -14793,36 +14703,36 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-11 09:42</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deducted</t>
+          <t xml:space="preserve">deferred</t>
         </is>
       </c>
       <c r="F24" s="4">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G24" s="4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="I24" s="4">
-        <v>350</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3</t>
+          <t xml:space="preserve">#2</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
@@ -14846,22 +14756,22 @@
         </is>
       </c>
       <c r="F25" s="4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G25" s="4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H25" s="4">
+        <v>900</v>
+      </c>
+      <c r="I25" s="4">
         <v>600</v>
-      </c>
-      <c r="I25" s="4">
-        <v>400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3</t>
+          <t xml:space="preserve">#2</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
@@ -14891,87 +14801,165 @@
         <v>250</v>
       </c>
       <c r="H26" s="4">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I26" s="4">
-        <v>150</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5</t>
+          <t xml:space="preserve">#3</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Motaung</t>
+          <t xml:space="preserve">Isaac Mbele</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deferred</t>
+          <t xml:space="preserve">deducted</t>
         </is>
       </c>
       <c r="F27" s="4">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G27" s="4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H27" s="4">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="I27" s="4">
-        <v>3000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">#3</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac Mbele</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deducted</t>
+        </is>
+      </c>
+      <c r="F28" s="4">
+        <v>250</v>
+      </c>
+      <c r="G28" s="4">
+        <v>250</v>
+      </c>
+      <c r="H28" s="4">
+        <v>400</v>
+      </c>
+      <c r="I28" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#5</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daniel Motaung</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deferred</t>
+        </is>
+      </c>
+      <c r="F29" s="4">
+        <v>500</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I29" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">#6</t>
         </is>
       </c>
-      <c r="B28" s="0" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Isaac Mbele</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-07 12:01</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">deferred</t>
         </is>
       </c>
-      <c r="F28" s="4">
+      <c r="F30" s="4">
         <v>600</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G30" s="4">
         <v>0</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H30" s="4">
         <v>600</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I30" s="4">
         <v>600</v>
       </c>
     </row>

--- a/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
+++ b/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
@@ -8879,10 +8879,10 @@
         <f>SUM(C11,E11,G11,I11,K11,M11,O11,Q11)</f>
       </c>
       <c r="T11" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U11" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V11" s="4">
         <f>MAX(0,T11-U11)</f>
@@ -14076,177 +14076,150 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joshua Motsamai Nteo</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Car Payment</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-19</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Car Payments — R1 000 deducted weekly from wages; the accumulated weekly amounts are paid over to Joshua on the 25th of every month (owner instruction Bernie Burness, 24 Sep 2026).</t>
+        </is>
+      </c>
+      <c r="F8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ongoing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL LOANS</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Loan #</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Employee</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Date given</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deductions from</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Reason</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Original amount</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Instalment</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Repaid to date</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Outstanding balance</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Due this week</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Frequency</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#5</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Daniel Motaung</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-23</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-05</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT SCan Hopital needs money upfront for Scan as medical aid paid the d</t>
-        </is>
-      </c>
-      <c r="F11" s="4">
-        <v>3000</v>
-      </c>
-      <c r="G11" s="4">
-        <v>500</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weekly</t>
-        </is>
-      </c>
-      <c r="L11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">paid</t>
-        </is>
-      </c>
-      <c r="M11" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marked PAID but ledger shows only R0,00 repaid of R3 000,00 — please check</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#1</t>
+          <t xml:space="preserve">#5</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erick Mpho Molefe</t>
+          <t xml:space="preserve">Daniel Motaung</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fix car Whatsapp -- send so we need to go check first because we still</t>
+          <t xml:space="preserve">CT SCan Hopital needs money upfront for Scan as medical aid paid the d</t>
         </is>
       </c>
       <c r="F12" s="4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G12" s="4">
         <v>500</v>
       </c>
       <c r="H12" s="4">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
@@ -14255,14 +14228,19 @@
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">paid</t>
+        </is>
+      </c>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marked PAID but ledger shows only R0,00 repaid of R3 000,00 — please check</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#7</t>
+          <t xml:space="preserve">#1</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
@@ -14272,33 +14250,33 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-08-08</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-08-08</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 Sep 2026 WhatsApp 07:15: "Goodmorning Mama, can I please have R600 </t>
+          <t xml:space="preserve">Fix car Whatsapp -- send so we need to go check first because we still</t>
         </is>
       </c>
       <c r="F13" s="4">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="4">
         <v>500</v>
       </c>
       <c r="H13" s="4">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I13" s="5">
         <v>500</v>
       </c>
       <c r="J13" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
@@ -14314,43 +14292,43 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2</t>
+          <t xml:space="preserve">#7</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac Mbele</t>
+          <t xml:space="preserve">Erick Mpho Molefe</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 August Morning mother this week I spent joo aim loan 300 hundred ple</t>
+          <t xml:space="preserve">22 Sep 2026 WhatsApp 07:15: "Goodmorning Mama, can I please have R600 </t>
         </is>
       </c>
       <c r="F14" s="4">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="G14" s="4">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H14" s="4">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J14" s="4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
@@ -14366,7 +14344,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3</t>
+          <t xml:space="preserve">#2</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -14376,33 +14354,33 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-17</t>
+          <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morning mother joo aim asking 600 hundred loan please</t>
+          <t xml:space="preserve">3 August Morning mother this week I spent joo aim loan 300 hundred ple</t>
         </is>
       </c>
       <c r="F15" s="4">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G15" s="4">
         <v>250</v>
       </c>
       <c r="H15" s="4">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="I15" s="5">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="J15" s="4">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
@@ -14418,7 +14396,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#6</t>
+          <t xml:space="preserve">#3</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
@@ -14428,33 +14406,33 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morning mother my kids are having a trip off 1500 but aim short of 600</t>
+          <t xml:space="preserve">Morning mother joo aim asking 600 hundred loan please</t>
         </is>
       </c>
       <c r="F16" s="4">
         <v>600</v>
       </c>
       <c r="G16" s="4">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="H16" s="4">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="I16" s="5">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="J16" s="4">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
@@ -14470,7 +14448,7 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#8</t>
+          <t xml:space="preserve">#6</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
@@ -14480,136 +14458,149 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 Sep 2026 WhatsApp 08:15: "Mother so like. Aim not well balanced abo</t>
+          <t xml:space="preserve">Morning mother my kids are having a trip off 1500 but aim short of 600</t>
         </is>
       </c>
       <c r="F17" s="4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G17" s="4">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H17" s="4">
         <v>0</v>
       </c>
       <c r="I17" s="5">
+        <v>600</v>
+      </c>
+      <c r="J17" s="4">
+        <v>600</v>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weekly</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#8</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac Mbele</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-26</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 Sep 2026 WhatsApp 08:15: "Mother so like. Aim not well balanced abo</t>
+        </is>
+      </c>
+      <c r="F18" s="4">
         <v>500</v>
       </c>
-      <c r="J17" s="4">
+      <c r="G18" s="4">
+        <v>250</v>
+      </c>
+      <c r="H18" s="4">
         <v>0</v>
       </c>
-      <c r="K17" s="0" t="inlineStr">
+      <c r="I18" s="5">
+        <v>500</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">weekly</t>
         </is>
       </c>
-      <c r="L17" s="0" t="inlineStr">
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">active</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">LOAN REPAYMENT HISTORY (all payrolls)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Loan #</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Employee</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Payroll week</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Recorded at</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Result</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Scheduled</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deducted</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Balance before</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Balance after</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#1</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erick Mpho Molefe</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-11 10:12</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deducted</t>
-        </is>
-      </c>
-      <c r="F21" s="4">
-        <v>500</v>
-      </c>
-      <c r="G21" s="4">
-        <v>500</v>
-      </c>
-      <c r="H21" s="4">
-        <v>2000</v>
-      </c>
-      <c r="I21" s="4">
-        <v>1500</v>
       </c>
     </row>
     <row r="22">
@@ -14625,12 +14616,12 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
+          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
+          <t xml:space="preserve">2026-08-11 10:12</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -14645,10 +14636,10 @@
         <v>500</v>
       </c>
       <c r="H22" s="4">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="4">
         <v>1500</v>
-      </c>
-      <c r="I22" s="4">
-        <v>1000</v>
       </c>
     </row>
     <row r="23">
@@ -14664,12 +14655,12 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
@@ -14684,49 +14675,49 @@
         <v>500</v>
       </c>
       <c r="H23" s="4">
+        <v>1500</v>
+      </c>
+      <c r="I23" s="4">
         <v>1000</v>
-      </c>
-      <c r="I23" s="4">
-        <v>500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2</t>
+          <t xml:space="preserve">#1</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac Mbele</t>
+          <t xml:space="preserve">Erick Mpho Molefe</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 09:42</t>
+          <t xml:space="preserve">2026-09-07 12:01</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deferred</t>
+          <t xml:space="preserve">deducted</t>
         </is>
       </c>
       <c r="F24" s="4">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G24" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H24" s="4">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I24" s="4">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25">
@@ -14742,30 +14733,30 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
+          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
+          <t xml:space="preserve">2026-08-11 09:42</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deducted</t>
+          <t xml:space="preserve">deferred</t>
         </is>
       </c>
       <c r="F25" s="4">
         <v>300</v>
       </c>
       <c r="G25" s="4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4">
         <v>900</v>
       </c>
       <c r="I25" s="4">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26">
@@ -14781,12 +14772,12 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
@@ -14795,22 +14786,22 @@
         </is>
       </c>
       <c r="F26" s="4">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G26" s="4">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H26" s="4">
+        <v>900</v>
+      </c>
+      <c r="I26" s="4">
         <v>600</v>
-      </c>
-      <c r="I26" s="4">
-        <v>350</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3</t>
+          <t xml:space="preserve">#2</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
@@ -14820,12 +14811,12 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
+          <t xml:space="preserve">2026-09-07 12:01</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
@@ -14834,16 +14825,16 @@
         </is>
       </c>
       <c r="F27" s="4">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G27" s="4">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H27" s="4">
         <v>600</v>
       </c>
       <c r="I27" s="4">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28">
@@ -14859,12 +14850,12 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
@@ -14873,27 +14864,27 @@
         </is>
       </c>
       <c r="F28" s="4">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G28" s="4">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H28" s="4">
+        <v>600</v>
+      </c>
+      <c r="I28" s="4">
         <v>400</v>
-      </c>
-      <c r="I28" s="4">
-        <v>150</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5</t>
+          <t xml:space="preserve">#3</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Motaung</t>
+          <t xml:space="preserve">Isaac Mbele</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -14908,31 +14899,31 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deferred</t>
+          <t xml:space="preserve">deducted</t>
         </is>
       </c>
       <c r="F29" s="4">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="G29" s="4">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H29" s="4">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="I29" s="4">
-        <v>3000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#6</t>
+          <t xml:space="preserve">#5</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac Mbele</t>
+          <t xml:space="preserve">Daniel Motaung</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -14951,15 +14942,54 @@
         </is>
       </c>
       <c r="F30" s="4">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G30" s="4">
         <v>0</v>
       </c>
       <c r="H30" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I30" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#6</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac Mbele</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deferred</t>
+        </is>
+      </c>
+      <c r="F31" s="4">
         <v>600</v>
       </c>
-      <c r="I30" s="4">
+      <c r="G31" s="4">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4">
+        <v>600</v>
+      </c>
+      <c r="I31" s="4">
         <v>600</v>
       </c>
     </row>

--- a/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
+++ b/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
@@ -8879,10 +8879,10 @@
         <f>SUM(C11,E11,G11,I11,K11,M11,O11,Q11)</f>
       </c>
       <c r="T11" s="4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U11" s="7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V11" s="4">
         <f>MAX(0,T11-U11)</f>
@@ -14076,150 +14076,177 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joshua Motsamai Nteo</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Car Payment</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-19</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Car Payments — R1 000 deducted weekly from wages; the accumulated weekly amounts are paid over to Joshua on the 25th of every month (owner instruction Bernie Burness, 24 Sep 2026).</t>
-        </is>
-      </c>
-      <c r="F8" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ongoing</t>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL LOANS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADDITIONAL LOANS</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loan #</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employee</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date given</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deductions from</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Original amount</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Instalment</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repaid to date</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outstanding balance</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Due this week</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frequency</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loan #</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Employee</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date given</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deductions from</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reason</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Original amount</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Instalment</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Repaid to date</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outstanding balance</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Due this week</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frequency</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Check</t>
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#5</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daniel Motaung</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-23</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-05</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT SCan Hopital needs money upfront for Scan as medical aid paid the d</t>
+        </is>
+      </c>
+      <c r="F11" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G11" s="4">
+        <v>500</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weekly</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paid</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marked PAID but ledger shows only R0,00 repaid of R3 000,00 — please check</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5</t>
+          <t xml:space="preserve">#1</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Motaung</t>
+          <t xml:space="preserve">Erick Mpho Molefe</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2026-08-08</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-08-08</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CT SCan Hopital needs money upfront for Scan as medical aid paid the d</t>
+          <t xml:space="preserve">Fix car Whatsapp -- send so we need to go check first because we still</t>
         </is>
       </c>
       <c r="F12" s="4">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G12" s="4">
         <v>500</v>
       </c>
       <c r="H12" s="4">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I12" s="5">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J12" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
@@ -14228,19 +14255,14 @@
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marked PAID but ledger shows only R0,00 repaid of R3 000,00 — please check</t>
+          <t xml:space="preserve">active</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#1</t>
+          <t xml:space="preserve">#7</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
@@ -14250,33 +14272,33 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fix car Whatsapp -- send so we need to go check first because we still</t>
+          <t xml:space="preserve">22 Sep 2026 WhatsApp 07:15: "Goodmorning Mama, can I please have R600 </t>
         </is>
       </c>
       <c r="F13" s="4">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G13" s="4">
         <v>500</v>
       </c>
       <c r="H13" s="4">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
         <v>500</v>
       </c>
       <c r="J13" s="4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
@@ -14292,43 +14314,43 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#7</t>
+          <t xml:space="preserve">#2</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erick Mpho Molefe</t>
+          <t xml:space="preserve">Isaac Mbele</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 Sep 2026 WhatsApp 07:15: "Goodmorning Mama, can I please have R600 </t>
+          <t xml:space="preserve">3 August Morning mother this week I spent joo aim loan 300 hundred ple</t>
         </is>
       </c>
       <c r="F14" s="4">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="G14" s="4">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H14" s="4">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="I14" s="5">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="J14" s="4">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
@@ -14344,7 +14366,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2</t>
+          <t xml:space="preserve">#3</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -14354,33 +14376,33 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11</t>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 August Morning mother this week I spent joo aim loan 300 hundred ple</t>
+          <t xml:space="preserve">Morning mother joo aim asking 600 hundred loan please</t>
         </is>
       </c>
       <c r="F15" s="4">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="G15" s="4">
         <v>250</v>
       </c>
       <c r="H15" s="4">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="I15" s="5">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="J15" s="4">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
@@ -14396,7 +14418,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3</t>
+          <t xml:space="preserve">#6</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
@@ -14406,33 +14428,33 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-17</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morning mother joo aim asking 600 hundred loan please</t>
+          <t xml:space="preserve">Morning mother my kids are having a trip off 1500 but aim short of 600</t>
         </is>
       </c>
       <c r="F16" s="4">
         <v>600</v>
       </c>
       <c r="G16" s="4">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H16" s="4">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="J16" s="4">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
@@ -14448,7 +14470,7 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#6</t>
+          <t xml:space="preserve">#8</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
@@ -14458,33 +14480,33 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morning mother my kids are having a trip off 1500 but aim short of 600</t>
+          <t xml:space="preserve">22 Sep 2026 WhatsApp 08:15: "Mother so like. Aim not well balanced abo</t>
         </is>
       </c>
       <c r="F17" s="4">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G17" s="4">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="H17" s="4">
         <v>0</v>
       </c>
       <c r="I17" s="5">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J17" s="4">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
@@ -14497,110 +14519,97 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#8</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Isaac Mbele</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-22</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-26</t>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 Sep 2026 WhatsApp 08:15: "Mother so like. Aim not well balanced abo</t>
-        </is>
-      </c>
-      <c r="F18" s="4">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAN REPAYMENT HISTORY (all payrolls)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loan #</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employee</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payroll week</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded at</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Result</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduled</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deducted</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance before</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance after</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#1</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erick Mpho Molefe</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11 10:12</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deducted</t>
+        </is>
+      </c>
+      <c r="F21" s="4">
         <v>500</v>
       </c>
-      <c r="G18" s="4">
-        <v>250</v>
-      </c>
-      <c r="H18" s="4">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5">
+      <c r="G21" s="4">
         <v>500</v>
       </c>
-      <c r="J18" s="4">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weekly</t>
-        </is>
-      </c>
-      <c r="L18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAN REPAYMENT HISTORY (all payrolls)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loan #</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Employee</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Payroll week</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recorded at</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Result</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scheduled</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deducted</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Balance before</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Balance after</t>
-        </is>
+      <c r="H21" s="4">
+        <v>2000</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1500</v>
       </c>
     </row>
     <row r="22">
@@ -14616,12 +14625,12 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 10:12</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -14636,10 +14645,10 @@
         <v>500</v>
       </c>
       <c r="H22" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I22" s="4">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
@@ -14655,12 +14664,12 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
+          <t xml:space="preserve">2026-09-07 12:01</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
@@ -14675,49 +14684,49 @@
         <v>500</v>
       </c>
       <c r="H23" s="4">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I23" s="4">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#1</t>
+          <t xml:space="preserve">#2</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erick Mpho Molefe</t>
+          <t xml:space="preserve">Isaac Mbele</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-11 09:42</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deducted</t>
+          <t xml:space="preserve">deferred</t>
         </is>
       </c>
       <c r="F24" s="4">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G24" s="4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I24" s="4">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25">
@@ -14733,30 +14742,30 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-08 → 2026-08-14</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 09:42</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deferred</t>
+          <t xml:space="preserve">deducted</t>
         </is>
       </c>
       <c r="F25" s="4">
         <v>300</v>
       </c>
       <c r="G25" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H25" s="4">
         <v>900</v>
       </c>
       <c r="I25" s="4">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26">
@@ -14772,12 +14781,12 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
+          <t xml:space="preserve">2026-09-07 12:01</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
@@ -14786,22 +14795,22 @@
         </is>
       </c>
       <c r="F26" s="4">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G26" s="4">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H26" s="4">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="I26" s="4">
-        <v>600</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2</t>
+          <t xml:space="preserve">#3</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
@@ -14811,12 +14820,12 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
+          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
+          <t xml:space="preserve">2026-08-16 13:37</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
@@ -14825,16 +14834,16 @@
         </is>
       </c>
       <c r="F27" s="4">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G27" s="4">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H27" s="4">
         <v>600</v>
       </c>
       <c r="I27" s="4">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28">
@@ -14850,12 +14859,12 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15 → 2026-08-21</t>
+          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 13:37</t>
+          <t xml:space="preserve">2026-09-07 12:01</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
@@ -14864,27 +14873,27 @@
         </is>
       </c>
       <c r="F28" s="4">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G28" s="4">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H28" s="4">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I28" s="4">
-        <v>400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#3</t>
+          <t xml:space="preserve">#5</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac Mbele</t>
+          <t xml:space="preserve">Daniel Motaung</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -14899,31 +14908,31 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">deducted</t>
+          <t xml:space="preserve">deferred</t>
         </is>
       </c>
       <c r="F29" s="4">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G29" s="4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="I29" s="4">
-        <v>150</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#5</t>
+          <t xml:space="preserve">#6</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Motaung</t>
+          <t xml:space="preserve">Isaac Mbele</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -14942,54 +14951,15 @@
         </is>
       </c>
       <c r="F30" s="4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G30" s="4">
         <v>0</v>
       </c>
       <c r="H30" s="4">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="I30" s="4">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#6</t>
-        </is>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Isaac Mbele</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-05 → 2026-09-11</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07 12:01</t>
-        </is>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deferred</t>
-        </is>
-      </c>
-      <c r="F31" s="4">
-        <v>600</v>
-      </c>
-      <c r="G31" s="4">
-        <v>0</v>
-      </c>
-      <c r="H31" s="4">
-        <v>600</v>
-      </c>
-      <c r="I31" s="4">
         <v>600</v>
       </c>
     </row>

--- a/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
+++ b/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
@@ -2643,7 +2643,7 @@
         <f>IF(N32&lt;&gt;"",N32,M32)</f>
       </c>
       <c r="P32" s="4">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="Q32" s="7"/>
       <c r="R32" s="5">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="T32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">System amount kept (gardener rate)</t>
+          <t xml:space="preserve">Gardener House work: 6 h × R62,50</t>
         </is>
       </c>
       <c r="U32" s="6"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">System amount kept (gardener rate)</t>
+          <t xml:space="preserve">Gardener House work: 8 h × R62,50</t>
         </is>
       </c>
       <c r="U33" s="6"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="T34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">System amount kept (gardener rate)</t>
+          <t xml:space="preserve">Gardener House work: 8 h × R62,50</t>
         </is>
       </c>
       <c r="U34" s="6"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="T35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">System amount kept (gardener rate)</t>
+          <t xml:space="preserve">Gardener House work: 8 h × R62,50</t>
         </is>
       </c>
       <c r="U35" s="6"/>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="T37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">System amount kept (gardener rate)</t>
+          <t xml:space="preserve">Gardener House work: 8 h × R62,50</t>
         </is>
       </c>
       <c r="U37" s="6"/>
@@ -5105,41 +5105,36 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>9770</v>
+        <v>9861</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
+          <t xml:space="preserve">Lebo Lebo</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
-        </is>
-      </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parys</t>
+          <t xml:space="preserve">Warehouse</t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free state</t>
+          <t xml:space="preserve">Highbury</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Golf day Set up</t>
+          <t xml:space="preserve">Offloading + Loading</t>
         </is>
       </c>
       <c r="I62" s="0" t="inlineStr">
@@ -5149,88 +5144,78 @@
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">07:00</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">18:00</t>
+          <t xml:space="preserve">13:25</t>
         </is>
       </c>
       <c r="L62" s="9">
-        <v>2</v>
+        <v>6.42</v>
       </c>
       <c r="M62" s="9">
-        <v>2</v>
+        <v>6.42</v>
       </c>
       <c r="N62" s="6"/>
       <c r="O62" s="10">
         <f>IF(N62&lt;&gt;"",N62,M62)</f>
       </c>
       <c r="P62" s="4">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="7"/>
       <c r="R62" s="5">
         <f>IF(Q62&lt;&gt;"",Q62,IF(N62&lt;&gt;"",IF(M62&gt;0,ROUND(P62*N62/M62,2),0),P62))</f>
       </c>
       <c r="S62" s="9">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="T62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 2 h × R95</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — HELD for owner approval — recommended Venue/event public holiday (Heritage Day): 6.42 h × R190 (R95 × 2) = R1 219,17; R0 until approved</t>
         </is>
       </c>
       <c r="U62" s="6"/>
-      <c r="W62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLEAR: worked 06:30–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
-        </is>
-      </c>
-      <c r="X62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No review needed</t>
+      <c r="V62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10149</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>9771</v>
+        <v>9862</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
+          <t xml:space="preserve">Lebo Lebo</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
-        </is>
-      </c>
-      <c r="E63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parys</t>
+          <t xml:space="preserve">Riverside sun + stonehaven + amstel arena</t>
         </is>
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free state</t>
+          <t xml:space="preserve">Vanderbiljpark + Soweto</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Golf day set up</t>
+          <t xml:space="preserve">Collections + drop off</t>
         </is>
       </c>
       <c r="I63" s="0" t="inlineStr">
@@ -5240,26 +5225,26 @@
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:00</t>
+          <t xml:space="preserve">07:00</t>
         </is>
       </c>
       <c r="K63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L63" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M63" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N63" s="6"/>
       <c r="O63" s="10">
         <f>IF(N63&lt;&gt;"",N63,M63)</f>
       </c>
       <c r="P63" s="4">
-        <v>95</v>
+        <v>855</v>
       </c>
       <c r="Q63" s="7"/>
       <c r="R63" s="5">
@@ -5270,24 +5255,14 @@
       </c>
       <c r="T63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 1 h × R95</t>
+          <t xml:space="preserve">Venue/event: 9 h × R95</t>
         </is>
       </c>
       <c r="U63" s="6"/>
-      <c r="W63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
-        </is>
-      </c>
-      <c r="X63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No review needed</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>9772</v>
+        <v>9770</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -5296,12 +5271,12 @@
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="E64" s="0" t="inlineStr">
@@ -5321,7 +5296,7 @@
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breakdown</t>
+          <t xml:space="preserve">Golf day Set up</t>
         </is>
       </c>
       <c r="I64" s="0" t="inlineStr">
@@ -5336,21 +5311,21 @@
       </c>
       <c r="K64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:00</t>
+          <t xml:space="preserve">18:00</t>
         </is>
       </c>
       <c r="L64" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M64" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N64" s="6"/>
       <c r="O64" s="10">
         <f>IF(N64&lt;&gt;"",N64,M64)</f>
       </c>
       <c r="P64" s="4">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="Q64" s="7"/>
       <c r="R64" s="5">
@@ -5361,13 +5336,13 @@
       </c>
       <c r="T64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 4 h × R95</t>
+          <t xml:space="preserve">Venue/event: 2 h × R95</t>
         </is>
       </c>
       <c r="U64" s="6"/>
       <c r="W64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
+          <t xml:space="preserve">CLEAR: worked 06:30–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
         </is>
       </c>
       <c r="X64" s="0" t="inlineStr">
@@ -5378,7 +5353,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>9769</v>
+        <v>9771</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -5387,27 +5362,32 @@
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday</t>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FNB Stadium</t>
+          <t xml:space="preserve">Parys</t>
         </is>
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannesburg</t>
+          <t xml:space="preserve">Free state</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breakdown</t>
+          <t xml:space="preserve">Golf day set up</t>
         </is>
       </c>
       <c r="I65" s="0" t="inlineStr">
@@ -5417,26 +5397,26 @@
       </c>
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:30</t>
+          <t xml:space="preserve">06:00</t>
         </is>
       </c>
       <c r="K65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">07:00</t>
         </is>
       </c>
       <c r="L65" s="9">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="M65" s="9">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="N65" s="6"/>
       <c r="O65" s="10">
         <f>IF(N65&lt;&gt;"",N65,M65)</f>
       </c>
       <c r="P65" s="4">
-        <v>902.5</v>
+        <v>95</v>
       </c>
       <c r="Q65" s="7"/>
       <c r="R65" s="5">
@@ -5447,14 +5427,24 @@
       </c>
       <c r="T65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 9.5 h × R95</t>
+          <t xml:space="preserve">Venue/event: 1 h × R95</t>
         </is>
       </c>
       <c r="U65" s="6"/>
+      <c r="W65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
+        </is>
+      </c>
+      <c r="X65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No review needed</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>9773</v>
+        <v>9772</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -5463,27 +5453,32 @@
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuesday</t>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="F66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wearhouse</t>
+          <t xml:space="preserve">Parys</t>
         </is>
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meyerton</t>
+          <t xml:space="preserve">Free state</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading</t>
+          <t xml:space="preserve">Breakdown</t>
         </is>
       </c>
       <c r="I66" s="0" t="inlineStr">
@@ -5493,49 +5488,54 @@
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:30</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">20:00</t>
         </is>
       </c>
       <c r="L66" s="9">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M66" s="9">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="N66" s="6"/>
       <c r="O66" s="10">
         <f>IF(N66&lt;&gt;"",N66,M66)</f>
       </c>
       <c r="P66" s="4">
-        <v>731.25</v>
+        <v>380</v>
       </c>
       <c r="Q66" s="7"/>
       <c r="R66" s="5">
         <f>IF(Q66&lt;&gt;"",Q66,IF(N66&lt;&gt;"",IF(M66&gt;0,ROUND(P66*N66/M66,2),0),P66))</f>
       </c>
       <c r="S66" s="9">
-        <v>81.25</v>
+        <v>95</v>
       </c>
       <c r="T66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse: 9.5 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 9 h × R81,25</t>
+          <t xml:space="preserve">Venue/event: 4 h × R95</t>
         </is>
       </c>
       <c r="U66" s="6"/>
-      <c r="V66" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#9954</t>
+      <c r="W66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
+        </is>
+      </c>
+      <c r="X66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No review needed</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>9837</v>
+        <v>9769</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -5544,27 +5544,27 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaal Boating Season</t>
+          <t xml:space="preserve">FNB Stadium</t>
         </is>
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vereeniging</t>
+          <t xml:space="preserve">Johannesburg</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set up</t>
+          <t xml:space="preserve">Breakdown</t>
         </is>
       </c>
       <c r="I67" s="0" t="inlineStr">
@@ -5611,7 +5611,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>9838</v>
+        <v>9773</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="F68" s="0" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="I68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse Team</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="J68" s="0" t="inlineStr">
@@ -5655,49 +5655,44 @@
       </c>
       <c r="K68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L68" s="9">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="M68" s="9">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="N68" s="6"/>
       <c r="O68" s="10">
         <f>IF(N68&lt;&gt;"",N68,M68)</f>
       </c>
       <c r="P68" s="4">
-        <v>1300</v>
+        <v>731.25</v>
       </c>
       <c r="Q68" s="7"/>
       <c r="R68" s="5">
         <f>IF(Q68&lt;&gt;"",Q68,IF(N68&lt;&gt;"",IF(M68&gt;0,ROUND(P68*N68/M68,2),0),P68))</f>
       </c>
       <c r="S68" s="9">
-        <v>162.5</v>
+        <v>81.25</v>
       </c>
       <c r="T68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — warehouse, hours set to 06:30–15:00 (no set-ups). 8 h × R162,50 = R1300</t>
+          <t xml:space="preserve">Warehouse: 9.5 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 9 h × R81,25</t>
         </is>
       </c>
       <c r="U68" s="6"/>
-      <c r="W68" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10143 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Patrick Ngozo worked 06:30–15:00. Held for owner approval.</t>
-        </is>
-      </c>
-      <c r="X68" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10143 DECIDED 8.00 h by Bernie Burness 2026-09-23 10:30: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day), owner set hours 06:30–15:00: 8.5 h − 0.5 h staff meeting = 8 h × R162,50 = R1 300,00</t>
+      <c r="V68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#9954</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>9839</v>
+        <v>9837</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -5706,27 +5701,27 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pretoria Country Club</t>
+          <t xml:space="preserve">Vaal Boating Season</t>
         </is>
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pretoria</t>
+          <t xml:space="preserve">Vereeniging</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set up Golf ⛳️  course</t>
+          <t xml:space="preserve">Set up</t>
         </is>
       </c>
       <c r="I69" s="0" t="inlineStr">
@@ -5773,132 +5768,122 @@
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>9831</v>
+        <v>9838</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon Moyo</t>
+          <t xml:space="preserve">Patrick Ngozo</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
-        </is>
-      </c>
-      <c r="E70" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parys Country Club</t>
+          <t xml:space="preserve">Wearhouse</t>
         </is>
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free State</t>
+          <t xml:space="preserve">Meyerton</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set up</t>
+          <t xml:space="preserve">Loading</t>
         </is>
       </c>
       <c r="I70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Warehouse Team</t>
         </is>
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">06:30</t>
         </is>
       </c>
       <c r="K70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">18:00</t>
+          <t xml:space="preserve">15:00</t>
         </is>
       </c>
       <c r="L70" s="9">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="M70" s="9">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="N70" s="6"/>
       <c r="O70" s="10">
         <f>IF(N70&lt;&gt;"",N70,M70)</f>
       </c>
       <c r="P70" s="4">
-        <v>190</v>
+        <v>1300</v>
       </c>
       <c r="Q70" s="7"/>
       <c r="R70" s="5">
         <f>IF(Q70&lt;&gt;"",Q70,IF(N70&lt;&gt;"",IF(M70&gt;0,ROUND(P70*N70/M70,2),0),P70))</f>
       </c>
       <c r="S70" s="9">
-        <v>95</v>
+        <v>162.5</v>
       </c>
       <c r="T70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 2 h × R95</t>
+          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — warehouse, hours set to 06:30–15:00 (no set-ups). 8 h × R162,50 = R1300</t>
         </is>
       </c>
       <c r="U70" s="6"/>
       <c r="W70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
+          <t xml:space="preserve">#10143 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Patrick Ngozo worked 06:30–15:00. Held for owner approval.</t>
         </is>
       </c>
       <c r="X70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No review needed</t>
+          <t xml:space="preserve">#10143 DECIDED 8.00 h by Bernie Burness 2026-09-23 10:30: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day), owner set hours 06:30–15:00: 8.5 h − 0.5 h staff meeting = 8 h × R162,50 = R1 300,00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>9830</v>
+        <v>9839</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon Moyo</t>
+          <t xml:space="preserve">Patrick Ngozo</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
-        </is>
-      </c>
-      <c r="E71" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parys Country Club</t>
+          <t xml:space="preserve">Pretoria Country Club</t>
         </is>
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free State</t>
+          <t xml:space="preserve">Pretoria</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breakdown</t>
+          <t xml:space="preserve">Set up Golf ⛳️  course</t>
         </is>
       </c>
       <c r="I71" s="0" t="inlineStr">
@@ -5908,26 +5893,26 @@
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">06:30</t>
+        </is>
+      </c>
+      <c r="K71" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">16:00</t>
         </is>
       </c>
-      <c r="K71" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21:00</t>
-        </is>
-      </c>
       <c r="L71" s="9">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="M71" s="9">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="N71" s="6"/>
       <c r="O71" s="10">
         <f>IF(N71&lt;&gt;"",N71,M71)</f>
       </c>
       <c r="P71" s="4">
-        <v>475</v>
+        <v>902.5</v>
       </c>
       <c r="Q71" s="7"/>
       <c r="R71" s="5">
@@ -5938,24 +5923,14 @@
       </c>
       <c r="T71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 5 h × R95</t>
+          <t xml:space="preserve">Venue/event: 9.5 h × R95</t>
         </is>
       </c>
       <c r="U71" s="6"/>
-      <c r="W71" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
-        </is>
-      </c>
-      <c r="X71" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No review needed</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>9836</v>
+        <v>9831</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -5964,27 +5939,32 @@
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday</t>
+          <t xml:space="preserve">Wednesday</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FNB Stadium</t>
+          <t xml:space="preserve">Parys Country Club</t>
         </is>
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannesburg</t>
+          <t xml:space="preserve">Free State</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breakdown</t>
+          <t xml:space="preserve">Set up</t>
         </is>
       </c>
       <c r="I72" s="0" t="inlineStr">
@@ -5994,26 +5974,26 @@
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="K72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">18:00</t>
         </is>
       </c>
       <c r="L72" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M72" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N72" s="6"/>
       <c r="O72" s="10">
         <f>IF(N72&lt;&gt;"",N72,M72)</f>
       </c>
       <c r="P72" s="4">
-        <v>855</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="7"/>
       <c r="R72" s="5">
@@ -6024,14 +6004,24 @@
       </c>
       <c r="T72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 9 h × R95</t>
+          <t xml:space="preserve">Venue/event: 2 h × R95</t>
         </is>
       </c>
       <c r="U72" s="6"/>
+      <c r="W72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
+        </is>
+      </c>
+      <c r="X72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No review needed</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>9835</v>
+        <v>9830</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -6040,27 +6030,32 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuesday</t>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse</t>
+          <t xml:space="preserve">Parys Country Club</t>
         </is>
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midvaal</t>
+          <t xml:space="preserve">Free State</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading</t>
+          <t xml:space="preserve">Breakdown</t>
         </is>
       </c>
       <c r="I73" s="0" t="inlineStr">
@@ -6070,49 +6065,54 @@
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="K73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">21:00</t>
         </is>
       </c>
       <c r="L73" s="9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M73" s="9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N73" s="6"/>
       <c r="O73" s="10">
         <f>IF(N73&lt;&gt;"",N73,M73)</f>
       </c>
       <c r="P73" s="4">
-        <v>690.63</v>
+        <v>475</v>
       </c>
       <c r="Q73" s="7"/>
       <c r="R73" s="5">
         <f>IF(Q73&lt;&gt;"",Q73,IF(N73&lt;&gt;"",IF(M73&gt;0,ROUND(P73*N73/M73,2),0),P73))</f>
       </c>
       <c r="S73" s="9">
-        <v>81.25</v>
+        <v>95</v>
       </c>
       <c r="T73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
+          <t xml:space="preserve">Venue/event: 5 h × R95</t>
         </is>
       </c>
       <c r="U73" s="6"/>
-      <c r="V73" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10063</t>
+      <c r="W73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times.</t>
+        </is>
+      </c>
+      <c r="X73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No review needed</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>9834</v>
+        <v>9836</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -6121,27 +6121,27 @@
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riverside sun</t>
+          <t xml:space="preserve">FNB Stadium</t>
         </is>
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanderbijlpark</t>
+          <t xml:space="preserve">Johannesburg</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set up</t>
+          <t xml:space="preserve">Breakdown</t>
         </is>
       </c>
       <c r="I74" s="0" t="inlineStr">
@@ -6188,7 +6188,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>9833</v>
+        <v>9835</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="F75" s="0" t="inlineStr">
@@ -6212,17 +6212,17 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannesburg</t>
+          <t xml:space="preserve">Midvaal</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set up</t>
+          <t xml:space="preserve">Loading</t>
         </is>
       </c>
       <c r="I75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse Team</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="J75" s="0" t="inlineStr">
@@ -6232,49 +6232,44 @@
       </c>
       <c r="K75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L75" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M75" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N75" s="6"/>
       <c r="O75" s="10">
         <f>IF(N75&lt;&gt;"",N75,M75)</f>
       </c>
       <c r="P75" s="4">
-        <v>1218.75</v>
+        <v>690.63</v>
       </c>
       <c r="Q75" s="7"/>
       <c r="R75" s="5">
         <f>IF(Q75&lt;&gt;"",Q75,IF(N75&lt;&gt;"",IF(M75&gt;0,ROUND(P75*N75/M75,2),0),P75))</f>
       </c>
       <c r="S75" s="9">
-        <v>162.5</v>
+        <v>81.25</v>
       </c>
       <c r="T75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — whole crew in the warehouse 07:00–15:00 (worker wrote Botanical Gardens, 16:00). 7.5 h × R162,50 = R1 218,75</t>
+          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
         </is>
       </c>
       <c r="U75" s="6"/>
-      <c r="W75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10060 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Solomon Moyo worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Botanical Gardens (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="X75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10060 DECIDED 7.50 h by Bernie Burness 2026-09-23 10:31: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — warehouse, hours set to 07:00–15:00 (worker wrote Botanical Gardens until 16:00): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1 218,75</t>
+      <c r="V75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10063</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>9832</v>
+        <v>9834</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -6283,12 +6278,12 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="F76" s="0" t="inlineStr">
@@ -6303,7 +6298,7 @@
       </c>
       <c r="H76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breakdown</t>
+          <t xml:space="preserve">Set up</t>
         </is>
       </c>
       <c r="I76" s="0" t="inlineStr">
@@ -6350,16 +6345,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>9815</v>
+        <v>9833</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
+          <t xml:space="preserve">Solomon Moyo</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -6367,14 +6362,9 @@
           <t xml:space="preserve">Thursday</t>
         </is>
       </c>
-      <c r="E77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
-        </is>
-      </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FNB</t>
+          <t xml:space="preserve">Warehouse</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
@@ -6394,130 +6384,130 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">07:00</t>
         </is>
       </c>
       <c r="K77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">18:00</t>
+          <t xml:space="preserve">15:00</t>
         </is>
       </c>
       <c r="L77" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M77" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N77" s="6"/>
       <c r="O77" s="10">
         <f>IF(N77&lt;&gt;"",N77,M77)</f>
       </c>
       <c r="P77" s="4">
-        <v>190</v>
+        <v>1218.75</v>
       </c>
       <c r="Q77" s="7"/>
       <c r="R77" s="5">
         <f>IF(Q77&lt;&gt;"",Q77,IF(N77&lt;&gt;"",IF(M77&gt;0,ROUND(P77*N77/M77,2),0),P77))</f>
       </c>
       <c r="S77" s="9">
-        <v>95</v>
+        <v>162.5</v>
       </c>
       <c r="T77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 2 h × R95</t>
+          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — whole crew in the warehouse 07:00–15:00 (worker wrote Botanical Gardens, 16:00). 7.5 h × R162,50 = R1 218,75</t>
         </is>
       </c>
       <c r="U77" s="6"/>
       <c r="W77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times. | #10074 Warehouse claimed — but the entry names “Johannesburg”: WAREHOUSE CLAIMED BUT THE ENTRY NAMES “Johannesburg”: Takavaudza Chokuda selected Warehouse Team at “FNB” for 2.00 h on Thu 17 Sep 2026, but wrote “Johannesburg” — that is a venue, not the warehouse. 6 workers were at a venue that day (Additional 5 hour shift - 17/09/2026 Parys Golf Day, Botanical garden Pretoria, FNB Stadium, Parys golf &amp; country Estate, Parys Country Club, Parys, Botanical gardens, Fnb stadium). If he was at “Johannesburg”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+          <t xml:space="preserve">#10060 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Solomon Moyo worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Botanical Gardens (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
         </is>
       </c>
       <c r="X77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10074 DECIDED by Bernie Burness 2026-09-23 11:01: Event/Venue rate chosen — shift #9815 R162,50 → R190,00 (Venue/event: 2 h × R95)</t>
+          <t xml:space="preserve">#10060 DECIDED 7.50 h by Bernie Burness 2026-09-23 10:31: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — warehouse, hours set to 07:00–15:00 (worker wrote Botanical Gardens until 16:00): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1 218,75</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>9821</v>
+        <v>9832</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
+          <t xml:space="preserve">Solomon Moyo</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-20</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunday</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">House</t>
+          <t xml:space="preserve">Riverside sun</t>
         </is>
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">henley</t>
+          <t xml:space="preserve">Vanderbijlpark</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Installing lights and garden  work</t>
+          <t xml:space="preserve">Breakdown</t>
         </is>
       </c>
       <c r="I78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">House/Garden</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">08:00</t>
+          <t xml:space="preserve">07:00</t>
         </is>
       </c>
       <c r="K78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">14:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L78" s="9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M78" s="9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N78" s="6"/>
       <c r="O78" s="10">
         <f>IF(N78&lt;&gt;"",N78,M78)</f>
       </c>
       <c r="P78" s="4">
-        <v>375</v>
+        <v>855</v>
       </c>
       <c r="Q78" s="7"/>
       <c r="R78" s="5">
         <f>IF(Q78&lt;&gt;"",Q78,IF(N78&lt;&gt;"",IF(M78&gt;0,ROUND(P78*N78/M78,2),0),P78))</f>
       </c>
       <c r="S78" s="9">
-        <v>62.5</v>
+        <v>95</v>
       </c>
       <c r="T78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Sunday house work 08:00–14:00 = 6 h × R62,50 = R375 (engine had paid 9 h)</t>
+          <t xml:space="preserve">Venue/event: 9 h × R95</t>
         </is>
       </c>
       <c r="U78" s="6"/>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>9816</v>
+        <v>9815</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -6526,27 +6516,32 @@
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday</t>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse</t>
+          <t xml:space="preserve">FNB</t>
         </is>
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henley-onklip</t>
+          <t xml:space="preserve">Johannesburg</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixing equipment</t>
+          <t xml:space="preserve">Set up</t>
         </is>
       </c>
       <c r="I79" s="0" t="inlineStr">
@@ -6556,54 +6551,54 @@
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="K79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">18:00</t>
         </is>
       </c>
       <c r="L79" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M79" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N79" s="6"/>
       <c r="O79" s="10">
         <f>IF(N79&lt;&gt;"",N79,M79)</f>
       </c>
       <c r="P79" s="4">
-        <v>690.63</v>
+        <v>190</v>
       </c>
       <c r="Q79" s="7"/>
       <c r="R79" s="5">
         <f>IF(Q79&lt;&gt;"",Q79,IF(N79&lt;&gt;"",IF(M79&gt;0,ROUND(P79*N79/M79,2),0),P79))</f>
       </c>
       <c r="S79" s="9">
-        <v>81.25</v>
+        <v>95</v>
       </c>
       <c r="T79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
+          <t xml:space="preserve">Venue/event: 2 h × R95</t>
         </is>
       </c>
       <c r="U79" s="6"/>
       <c r="W79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9955 Crew pattern — 8 of 9 at a venue, this one says Warehouse: CREW PATTERN: 8 of 9 workers were at a venue on Mon 21 Sep 2026 (FNB Stadium, FNB strike down, Fnb stadium) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
+          <t xml:space="preserve">CLEAR: worked 07:00–16:00 that day (paid in payroll n/a); these hours are outside those times. | #10074 Warehouse claimed — but the entry names “Johannesburg”: WAREHOUSE CLAIMED BUT THE ENTRY NAMES “Johannesburg”: Takavaudza Chokuda selected Warehouse Team at “FNB” for 2.00 h on Thu 17 Sep 2026, but wrote “Johannesburg” — that is a venue, not the warehouse. 6 workers were at a venue that day (Additional 5 hour shift - 17/09/2026 Parys Golf Day, Botanical garden Pretoria, FNB Stadium, Parys golf &amp; country Estate, Parys Country Club, Parys, Botanical gardens, Fnb stadium). If he was at “Johannesburg”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
         </is>
       </c>
       <c r="X79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#9955 DECIDED 9.00 h by Bernie Burness 2026-09-23 11:01: WAREHOUSE — R81,25/h chosen by Bernie Burness for draft #830 — will pay R690,63 when final-submitted (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">#10074 DECIDED by Bernie Burness 2026-09-23 11:01: Event/Venue rate chosen — shift #9815 R162,50 → R190,00 (Venue/event: 2 h × R95)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>9820</v>
+        <v>9821</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -6612,74 +6607,74 @@
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-20</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuesday</t>
+          <t xml:space="preserve">Sunday</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse</t>
+          <t xml:space="preserve">House</t>
         </is>
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henley-onklip</t>
+          <t xml:space="preserve">henley</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Installing lights and garden  work</t>
         </is>
       </c>
       <c r="I80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse Team</t>
+          <t xml:space="preserve">House/Garden</t>
         </is>
       </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00</t>
+          <t xml:space="preserve">08:00</t>
         </is>
       </c>
       <c r="K80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">14:00</t>
         </is>
       </c>
       <c r="L80" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M80" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N80" s="6"/>
       <c r="O80" s="10">
         <f>IF(N80&lt;&gt;"",N80,M80)</f>
       </c>
       <c r="P80" s="4">
-        <v>690.63</v>
+        <v>450</v>
       </c>
       <c r="Q80" s="7"/>
       <c r="R80" s="5">
         <f>IF(Q80&lt;&gt;"",Q80,IF(N80&lt;&gt;"",IF(M80&gt;0,ROUND(P80*N80/M80,2),0),P80))</f>
       </c>
       <c r="S80" s="9">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="T80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
+          <t xml:space="preserve">OWNER CORRECTION: Owner 24 Sep: Sunday house work 08:00–14:00 = 6 h × R62,50 × 1.2 (Sunday) = 6 h × R75 = R450,00 (was R375 — Sunday ×1.2 had been left off)</t>
         </is>
       </c>
       <c r="U80" s="6"/>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>9819</v>
+        <v>9816</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -6688,27 +6683,27 @@
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riverside</t>
+          <t xml:space="preserve">Warehouse</t>
         </is>
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The vaal</t>
+          <t xml:space="preserve">Henley-onklip</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set up</t>
+          <t xml:space="preserve">Fixing equipment</t>
         </is>
       </c>
       <c r="I81" s="0" t="inlineStr">
@@ -6737,35 +6732,35 @@
         <f>IF(N81&lt;&gt;"",N81,M81)</f>
       </c>
       <c r="P81" s="4">
-        <v>855</v>
+        <v>690.63</v>
       </c>
       <c r="Q81" s="7"/>
       <c r="R81" s="5">
         <f>IF(Q81&lt;&gt;"",Q81,IF(N81&lt;&gt;"",IF(M81&gt;0,ROUND(P81*N81/M81,2),0),P81))</f>
       </c>
       <c r="S81" s="9">
-        <v>95</v>
+        <v>81.25</v>
       </c>
       <c r="T81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 9 h × R95</t>
+          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
         </is>
       </c>
       <c r="U81" s="6"/>
       <c r="W81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10075 Warehouse claimed — but the entry names “The vaal”: WAREHOUSE CLAIMED BUT THE ENTRY NAMES “The vaal”: Takavaudza Chokuda selected Warehouse Team at “Riverside” for 9.00 h on Wed 23 Sep 2026, but wrote “The vaal” — that is a venue, not the warehouse. 6 workers were at a venue that day (Work with the Team, wharehouse, Set up vaal Boating, Riverside sun, Vaal Boating Season, Stone Haven And Riverside Sun). If he was at “The vaal”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+          <t xml:space="preserve">#9955 Crew pattern — 8 of 9 at a venue, this one says Warehouse: CREW PATTERN: 8 of 9 workers were at a venue on Mon 21 Sep 2026 (FNB Stadium, FNB strike down, Fnb stadium) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
         </is>
       </c>
       <c r="X81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10075 DECIDED by Bernie Burness 2026-09-23 11:01: Event/Venue rate chosen — shift #9819 R690,63 → R855,00 (Venue/event: 9 h × R95)</t>
+          <t xml:space="preserve">#9955 DECIDED 9.00 h by Bernie Burness 2026-09-23 11:01: WAREHOUSE — R81,25/h chosen by Bernie Burness for draft #830 — will pay R690,63 when final-submitted (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>9818</v>
+        <v>9820</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -6774,12 +6769,12 @@
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="F82" s="0" t="inlineStr">
@@ -6809,49 +6804,39 @@
       </c>
       <c r="K82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L82" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M82" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N82" s="6"/>
       <c r="O82" s="10">
         <f>IF(N82&lt;&gt;"",N82,M82)</f>
       </c>
       <c r="P82" s="4">
-        <v>1218.75</v>
+        <v>690.63</v>
       </c>
       <c r="Q82" s="7"/>
       <c r="R82" s="5">
         <f>IF(Q82&lt;&gt;"",Q82,IF(N82&lt;&gt;"",IF(M82&gt;0,ROUND(P82*N82/M82,2),0),P82))</f>
       </c>
       <c r="S82" s="9">
-        <v>162.5</v>
+        <v>81.25</v>
       </c>
       <c r="T82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — warehouse, hours set to 07:00–15:00 (no set-ups). 7.5 h × R162,50 = R1218.75</t>
+          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
         </is>
       </c>
       <c r="U82" s="6"/>
-      <c r="W82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10039 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Takavaudza Chokuda worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Warehouse Team). Public-holiday work is not paid automatically. Recommended: Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="X82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10039 DECIDED 7.50 h by Bernie Burness 2026-09-23 10:32: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>9817</v>
+        <v>9819</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -6860,27 +6845,27 @@
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse</t>
+          <t xml:space="preserve">Riverside</t>
         </is>
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henley-onklip</t>
+          <t xml:space="preserve">The vaal</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Set up</t>
         </is>
       </c>
       <c r="I83" s="0" t="inlineStr">
@@ -6909,69 +6894,69 @@
         <f>IF(N83&lt;&gt;"",N83,M83)</f>
       </c>
       <c r="P83" s="4">
-        <v>690.63</v>
+        <v>855</v>
       </c>
       <c r="Q83" s="7"/>
       <c r="R83" s="5">
         <f>IF(Q83&lt;&gt;"",Q83,IF(N83&lt;&gt;"",IF(M83&gt;0,ROUND(P83*N83/M83,2),0),P83))</f>
       </c>
       <c r="S83" s="9">
-        <v>81.25</v>
+        <v>95</v>
       </c>
       <c r="T83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
+          <t xml:space="preserve">Venue/event: 9 h × R95</t>
         </is>
       </c>
       <c r="U83" s="6"/>
       <c r="W83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10076 Crew pattern — 7 of 8 at a venue, this one says Warehouse: CREW PATTERN: 7 of 8 workers were at a venue on Fri 25 Sep 2026 (The Capital Sandton and Bonitical Emmarentia, Pretoria country club, Botanical, Vaal Boating, Riverside sun, Pretoria Country Club, Capital hotel / botanical gardens JHB) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
+          <t xml:space="preserve">#10075 Warehouse claimed — but the entry names “The vaal”: WAREHOUSE CLAIMED BUT THE ENTRY NAMES “The vaal”: Takavaudza Chokuda selected Warehouse Team at “Riverside” for 9.00 h on Wed 23 Sep 2026, but wrote “The vaal” — that is a venue, not the warehouse. 6 workers were at a venue that day (Work with the Team, wharehouse, Set up vaal Boating, Riverside sun, Vaal Boating Season, Stone Haven And Riverside Sun). If he was at “The vaal”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
         </is>
       </c>
       <c r="X83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10076 DECIDED by Bernie Burness 2026-09-23 11:01: Warehouse rate chosen — shift #9817 R690,63 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+          <t xml:space="preserve">#10075 DECIDED by Bernie Burness 2026-09-23 11:01: Event/Venue rate chosen — shift #9819 R690,63 → R855,00 (Venue/event: 9 h × R95)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>9840</v>
+        <v>9818</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FNB Stadium and Warehouse</t>
+          <t xml:space="preserve">Warehouse</t>
         </is>
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannesburg / Highbury</t>
+          <t xml:space="preserve">Henley-onklip</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scorpion Kings Strike Down and Offloading</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="I84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Warehouse Team</t>
         </is>
       </c>
       <c r="J84" s="0" t="inlineStr">
@@ -6981,58 +6966,63 @@
       </c>
       <c r="K84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">15:00</t>
         </is>
       </c>
       <c r="L84" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M84" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N84" s="6"/>
       <c r="O84" s="10">
         <f>IF(N84&lt;&gt;"",N84,M84)</f>
       </c>
       <c r="P84" s="4">
-        <v>855</v>
+        <v>1218.75</v>
       </c>
       <c r="Q84" s="7"/>
       <c r="R84" s="5">
         <f>IF(Q84&lt;&gt;"",Q84,IF(N84&lt;&gt;"",IF(M84&gt;0,ROUND(P84*N84/M84,2),0),P84))</f>
       </c>
       <c r="S84" s="9">
-        <v>95</v>
+        <v>162.5</v>
       </c>
       <c r="T84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 9 h × R95</t>
+          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — warehouse, hours set to 07:00–15:00 (no set-ups). 7.5 h × R162,50 = R1218.75</t>
         </is>
       </c>
       <c r="U84" s="6"/>
-      <c r="V84" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10080</t>
+      <c r="W84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10039 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Takavaudza Chokuda worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Warehouse Team). Public-holiday work is not paid automatically. Recommended: Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50. R0 is paid until the owner approves or declines.</t>
+        </is>
+      </c>
+      <c r="X84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10039 DECIDED 7.50 h by Bernie Burness 2026-09-23 10:32: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>9844</v>
+        <v>9817</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuesday</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="F85" s="0" t="inlineStr">
@@ -7042,17 +7032,17 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highbury</t>
+          <t xml:space="preserve">Henley-onklip</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offloading ,Loading and Cleaning</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="I85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Warehouse Team</t>
         </is>
       </c>
       <c r="J85" s="0" t="inlineStr">
@@ -7091,15 +7081,20 @@
         </is>
       </c>
       <c r="U85" s="6"/>
-      <c r="V85" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10087</t>
+      <c r="W85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10076 Crew pattern — 7 of 8 at a venue, this one says Warehouse: CREW PATTERN: 7 of 8 workers were at a venue on Fri 25 Sep 2026 (The Capital Sandton and Bonitical Emmarentia, Pretoria country club, Botanical, Vaal Boating, Riverside sun, Pretoria Country Club, Capital hotel / botanical gardens JHB) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
+        </is>
+      </c>
+      <c r="X85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10076 DECIDED by Bernie Burness 2026-09-23 11:01: Warehouse rate chosen — shift #9817 R690,63 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>9843</v>
+        <v>9840</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -7108,27 +7103,27 @@
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stone Haven And Riverside Sun</t>
+          <t xml:space="preserve">FNB Stadium and Warehouse</t>
         </is>
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanderbijlpark Vaal</t>
+          <t xml:space="preserve">Johannesburg / Highbury</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set Up Castle Lager</t>
+          <t xml:space="preserve">Scorpion Kings Strike Down and Offloading</t>
         </is>
       </c>
       <c r="I86" s="0" t="inlineStr">
@@ -7172,10 +7167,15 @@
         </is>
       </c>
       <c r="U86" s="6"/>
+      <c r="V86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10080</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>9842</v>
+        <v>9844</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="F87" s="0" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="H87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offloading and Loading</t>
+          <t xml:space="preserve">Offloading ,Loading and Cleaning</t>
         </is>
       </c>
       <c r="I87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse Team</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="J87" s="0" t="inlineStr">
@@ -7219,54 +7219,44 @@
       </c>
       <c r="K87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L87" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M87" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N87" s="6"/>
       <c r="O87" s="10">
         <f>IF(N87&lt;&gt;"",N87,M87)</f>
       </c>
       <c r="P87" s="4">
-        <v>1218.75</v>
+        <v>690.63</v>
       </c>
       <c r="Q87" s="7"/>
       <c r="R87" s="5">
         <f>IF(Q87&lt;&gt;"",Q87,IF(N87&lt;&gt;"",IF(M87&gt;0,ROUND(P87*N87/M87,2),0),P87))</f>
       </c>
       <c r="S87" s="9">
-        <v>162.5</v>
+        <v>81.25</v>
       </c>
       <c r="T87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — warehouse, hours set to 07:00–15:00 (no set-ups). 7.5 h × R162,50 = R1218.75</t>
+          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
         </is>
       </c>
       <c r="U87" s="6"/>
       <c r="V87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">#10084</t>
-        </is>
-      </c>
-      <c r="W87" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10142 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Thandanani Nkala worked 07:00–15:00. Held for owner approval.</t>
-        </is>
-      </c>
-      <c r="X87" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10142 DECIDED 7.50 h by Bernie Burness 2026-09-23 10:32: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
+          <t xml:space="preserve">#10087</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -7275,27 +7265,27 @@
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse</t>
+          <t xml:space="preserve">Stone Haven And Riverside Sun</t>
         </is>
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highbury</t>
+          <t xml:space="preserve">Vanderbijlpark Vaal</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offloading and Loading</t>
+          <t xml:space="preserve">Set Up Castle Lager</t>
         </is>
       </c>
       <c r="I88" s="0" t="inlineStr">
@@ -7324,39 +7314,34 @@
         <f>IF(N88&lt;&gt;"",N88,M88)</f>
       </c>
       <c r="P88" s="4">
-        <v>690.63</v>
+        <v>855</v>
       </c>
       <c r="Q88" s="7"/>
       <c r="R88" s="5">
         <f>IF(Q88&lt;&gt;"",Q88,IF(N88&lt;&gt;"",IF(M88&gt;0,ROUND(P88*N88/M88,2),0),P88))</f>
       </c>
       <c r="S88" s="9">
-        <v>81.25</v>
+        <v>95</v>
       </c>
       <c r="T88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
+          <t xml:space="preserve">Venue/event: 9 h × R95</t>
         </is>
       </c>
       <c r="U88" s="6"/>
-      <c r="V88" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10082</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>9796</v>
+        <v>9842</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thina Dyani</t>
+          <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -7364,95 +7349,95 @@
           <t xml:space="preserve">Thursday</t>
         </is>
       </c>
-      <c r="E89" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
-        </is>
-      </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additional 5 hour shift - 17/09/2026 Parys Golf Day</t>
+          <t xml:space="preserve">Warehouse</t>
         </is>
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parys</t>
+          <t xml:space="preserve">Highbury</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strike down</t>
+          <t xml:space="preserve">Offloading and Loading</t>
         </is>
       </c>
       <c r="I89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Warehouse Team</t>
         </is>
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">07:00</t>
         </is>
       </c>
       <c r="K89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">21:00</t>
+          <t xml:space="preserve">15:00</t>
         </is>
       </c>
       <c r="L89" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M89" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N89" s="6"/>
       <c r="O89" s="10">
         <f>IF(N89&lt;&gt;"",N89,M89)</f>
       </c>
       <c r="P89" s="4">
-        <v>475</v>
+        <v>1218.75</v>
       </c>
       <c r="Q89" s="7"/>
       <c r="R89" s="5">
         <f>IF(Q89&lt;&gt;"",Q89,IF(N89&lt;&gt;"",IF(M89&gt;0,ROUND(P89*N89/M89,2),0),P89))</f>
       </c>
       <c r="S89" s="9">
-        <v>95</v>
+        <v>162.5</v>
       </c>
       <c r="T89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venue/event: 5 h × R95</t>
+          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day — warehouse, hours set to 07:00–15:00 (no set-ups). 7.5 h × R162,50 = R1218.75</t>
         </is>
       </c>
       <c r="U89" s="6"/>
+      <c r="V89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10084</t>
+        </is>
+      </c>
       <c r="W89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLEAR: nothing else paid for this day.</t>
+          <t xml:space="preserve">#10142 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Thandanani Nkala worked 07:00–15:00. Held for owner approval.</t>
         </is>
       </c>
       <c r="X89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No review needed</t>
+          <t xml:space="preserve">#10142 DECIDED 7.50 h by Bernie Burness 2026-09-23 10:32: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>9802</v>
+        <v>9841</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+          <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-19</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saturday</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="F90" s="0" t="inlineStr">
@@ -7462,12 +7447,12 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henley on klip</t>
+          <t xml:space="preserve">Highbury</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleaning and re-packing</t>
+          <t xml:space="preserve">Offloading and Loading</t>
         </is>
       </c>
       <c r="I90" s="0" t="inlineStr">
@@ -7477,120 +7462,140 @@
       </c>
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:45</t>
+          <t xml:space="preserve">07:00</t>
         </is>
       </c>
       <c r="K90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L90" s="9">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="M90" s="9">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="N90" s="6"/>
       <c r="O90" s="10">
         <f>IF(N90&lt;&gt;"",N90,M90)</f>
       </c>
       <c r="P90" s="4">
-        <v>640</v>
+        <v>690.63</v>
       </c>
       <c r="Q90" s="7"/>
       <c r="R90" s="5">
         <f>IF(Q90&lt;&gt;"",Q90,IF(N90&lt;&gt;"",IF(M90&gt;0,ROUND(P90*N90/M90,2),0),P90))</f>
       </c>
       <c r="S90" s="9">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="T90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petrus Saturday: R640 set day rate (06–16)</t>
+          <t xml:space="preserve">Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25</t>
         </is>
       </c>
       <c r="U90" s="6"/>
+      <c r="V90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10082</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>9803</v>
+        <v>9796</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+          <t xml:space="preserve">Thina Dyani</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday</t>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="F91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse</t>
+          <t xml:space="preserve">Additional 5 hour shift - 17/09/2026 Parys Golf Day</t>
         </is>
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henley on klip</t>
+          <t xml:space="preserve">Parys</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading, offloading &amp; recieving</t>
+          <t xml:space="preserve">Strike down</t>
         </is>
       </c>
       <c r="I91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse Team</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:30</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="K91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">21:00</t>
         </is>
       </c>
       <c r="L91" s="9">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="M91" s="9">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="N91" s="6"/>
       <c r="O91" s="10">
         <f>IF(N91&lt;&gt;"",N91,M91)</f>
       </c>
       <c r="P91" s="4">
-        <v>640</v>
+        <v>475</v>
       </c>
       <c r="Q91" s="7"/>
       <c r="R91" s="5">
         <f>IF(Q91&lt;&gt;"",Q91,IF(N91&lt;&gt;"",IF(M91&gt;0,ROUND(P91*N91/M91,2),0),P91))</f>
       </c>
       <c r="S91" s="9">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="T91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petrus weekday: R640 set day rate (06–16)</t>
+          <t xml:space="preserve">Venue/event: 5 h × R95</t>
         </is>
       </c>
       <c r="U91" s="6"/>
+      <c r="W91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLEAR: nothing else paid for this day.</t>
+        </is>
+      </c>
+      <c r="X91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No review needed</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>9804</v>
+        <v>9802</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -7599,12 +7604,12 @@
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuesday</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="F92" s="0" t="inlineStr">
@@ -7619,29 +7624,29 @@
       </c>
       <c r="H92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading, washing of Gazebos and recieving</t>
+          <t xml:space="preserve">Cleaning and re-packing</t>
         </is>
       </c>
       <c r="I92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse Team</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:30</t>
+          <t xml:space="preserve">06:45</t>
         </is>
       </c>
       <c r="K92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00</t>
+          <t xml:space="preserve">12:00</t>
         </is>
       </c>
       <c r="L92" s="9">
-        <v>9.5</v>
+        <v>5.25</v>
       </c>
       <c r="M92" s="9">
-        <v>9.5</v>
+        <v>5.25</v>
       </c>
       <c r="N92" s="6"/>
       <c r="O92" s="10">
@@ -7655,18 +7660,18 @@
         <f>IF(Q92&lt;&gt;"",Q92,IF(N92&lt;&gt;"",IF(M92&gt;0,ROUND(P92*N92/M92,2),0),P92))</f>
       </c>
       <c r="S92" s="9">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="T92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petrus weekday: R640 set day rate (06–16)</t>
+          <t xml:space="preserve">Petrus Saturday: R640 set day rate (06–16)</t>
         </is>
       </c>
       <c r="U92" s="6"/>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>9810</v>
+        <v>9803</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -7675,12 +7680,12 @@
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="F93" s="0" t="inlineStr">
@@ -7695,12 +7700,12 @@
       </c>
       <c r="H93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Packing &amp; Loading and re-packing</t>
+          <t xml:space="preserve">Loading, offloading &amp; recieving</t>
         </is>
       </c>
       <c r="I93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Warehouse Team</t>
         </is>
       </c>
       <c r="J93" s="0" t="inlineStr">
@@ -7742,7 +7747,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>9813</v>
+        <v>9804</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -7751,12 +7756,12 @@
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thursday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="F94" s="0" t="inlineStr">
@@ -7771,12 +7776,12 @@
       </c>
       <c r="H94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleaning &amp; repacking</t>
+          <t xml:space="preserve">Loading, washing of Gazebos and recieving</t>
         </is>
       </c>
       <c r="I94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal</t>
+          <t xml:space="preserve">Warehouse Team</t>
         </is>
       </c>
       <c r="J94" s="0" t="inlineStr">
@@ -7786,49 +7791,39 @@
       </c>
       <c r="K94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">14:00</t>
+          <t xml:space="preserve">16:00</t>
         </is>
       </c>
       <c r="L94" s="9">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M94" s="9">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="N94" s="6"/>
       <c r="O94" s="10">
         <f>IF(N94&lt;&gt;"",N94,M94)</f>
       </c>
       <c r="P94" s="4">
-        <v>1120</v>
+        <v>640</v>
       </c>
       <c r="Q94" s="7"/>
       <c r="R94" s="5">
         <f>IF(Q94&lt;&gt;"",Q94,IF(N94&lt;&gt;"",IF(M94&gt;0,ROUND(P94*N94/M94,2),0),P94))</f>
       </c>
       <c r="S94" s="9">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="T94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day hours set to 06:30–14:00 (owner: worked till about 14:00 — TRIPLE-CHECK next week). 7.5 h − 0.5 h meeting = 7 h × R160 = R1 120</t>
+          <t xml:space="preserve">Petrus weekday: R640 set day rate (06–16)</t>
         </is>
       </c>
       <c r="U94" s="6"/>
-      <c r="W94" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10033 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Tsotlego Petrus Malakoane worked 06:30–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Normal). Public-holiday work is not paid automatically. Recommended: Petrus public holiday (Heritage Day): no fixed day — 9.5 h × R160 (R80 × 2) = R1 520,00. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="X94" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#10033 DECIDED 7.00 h by Bernie Burness 2026-09-23 11:02: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 06:30–14:00, meeting deducted: 7 h × R160 = R1 120,00. Owner not 100% sure of the end time — CONFIRM NEXT WEEK.</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>9814</v>
+        <v>9810</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -7837,12 +7832,12 @@
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="F95" s="0" t="inlineStr">
@@ -7857,7 +7852,7 @@
       </c>
       <c r="H95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispatch of a collection for a client</t>
+          <t xml:space="preserve">Packing &amp; Loading and re-packing</t>
         </is>
       </c>
       <c r="I95" s="0" t="inlineStr">
@@ -7902,26 +7897,188 @@
       </c>
       <c r="U95" s="6"/>
     </row>
+    <row r="96">
+      <c r="A96" s="0">
+        <v>9813</v>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henley on klip</t>
+        </is>
+      </c>
+      <c r="H96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cleaning &amp; repacking</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normal</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30</t>
+        </is>
+      </c>
+      <c r="K96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00</t>
+        </is>
+      </c>
+      <c r="L96" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="M96" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="N96" s="6"/>
+      <c r="O96" s="10">
+        <f>IF(N96&lt;&gt;"",N96,M96)</f>
+      </c>
+      <c r="P96" s="4">
+        <v>1120</v>
+      </c>
+      <c r="Q96" s="7"/>
+      <c r="R96" s="5">
+        <f>IF(Q96&lt;&gt;"",Q96,IF(N96&lt;&gt;"",IF(M96&gt;0,ROUND(P96*N96/M96,2),0),P96))</f>
+      </c>
+      <c r="S96" s="9">
+        <v>160</v>
+      </c>
+      <c r="T96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OWNER CORRECTION: Owner 23 Sep: Heritage Day hours set to 06:30–14:00 (owner: worked till about 14:00 — TRIPLE-CHECK next week). 7.5 h − 0.5 h meeting = 7 h × R160 = R1 120</t>
+        </is>
+      </c>
+      <c r="U96" s="6"/>
+      <c r="W96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10033 Public holiday (Heritage Day) — owner to approve or decline: PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Tsotlego Petrus Malakoane worked 06:30–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Normal). Public-holiday work is not paid automatically. Recommended: Petrus public holiday (Heritage Day): no fixed day — 9.5 h × R160 (R80 × 2) = R1 520,00. R0 is paid until the owner approves or declines.</t>
+        </is>
+      </c>
+      <c r="X96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#10033 DECIDED 7.00 h by Bernie Burness 2026-09-23 11:02: Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 06:30–14:00, meeting deducted: 7 h × R160 = R1 120,00. Owner not 100% sure of the end time — CONFIRM NEXT WEEK.</t>
+        </is>
+      </c>
+    </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" s="0">
+        <v>9814</v>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-25</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Friday</t>
+        </is>
+      </c>
+      <c r="F97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henley on klip</t>
+        </is>
+      </c>
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch of a collection for a client</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normal</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30</t>
+        </is>
+      </c>
+      <c r="K97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00</t>
+        </is>
+      </c>
+      <c r="L97" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="M97" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="N97" s="6"/>
+      <c r="O97" s="10">
+        <f>IF(N97&lt;&gt;"",N97,M97)</f>
+      </c>
+      <c r="P97" s="4">
+        <v>640</v>
+      </c>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="5">
+        <f>IF(Q97&lt;&gt;"",Q97,IF(N97&lt;&gt;"",IF(M97&gt;0,ROUND(P97*N97/M97,2),0),P97))</f>
+      </c>
+      <c r="S97" s="9">
+        <v>55</v>
+      </c>
+      <c r="T97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Petrus weekday: R640 set day rate (06–16)</t>
+        </is>
+      </c>
+      <c r="U97" s="6"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GRAND TOTAL</t>
         </is>
       </c>
-      <c r="L97" s="10">
-        <f>SUM(L5:L95)</f>
-      </c>
-      <c r="M97" s="10">
-        <f>SUM(M5:M95)</f>
-      </c>
-      <c r="O97" s="10">
-        <f>SUM(O5:O95)</f>
-      </c>
-      <c r="P97" s="5">
-        <f>SUM(P5:P95)</f>
-      </c>
-      <c r="R97" s="5">
-        <f>SUM(R5:R95)</f>
+      <c r="L99" s="10">
+        <f>SUM(L5:L97)</f>
+      </c>
+      <c r="M99" s="10">
+        <f>SUM(M5:M97)</f>
+      </c>
+      <c r="O99" s="10">
+        <f>SUM(O5:O97)</f>
+      </c>
+      <c r="P99" s="5">
+        <f>SUM(P5:P97)</f>
+      </c>
+      <c r="R99" s="5">
+        <f>SUM(R5:R97)</f>
       </c>
     </row>
   </sheetData>
@@ -8230,46 +8387,46 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C4" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B4&gt;0,ROUND(B4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B4/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B4&gt;0,ROUND(B4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B4/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D4" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E4" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D4&gt;0,ROUND(D4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D4/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D4&gt;0,ROUND(D4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D4/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F4" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G4" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F4&gt;0,ROUND(F4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F4/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F4&gt;0,ROUND(F4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F4/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H4" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I4" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H4&gt;0,ROUND(H4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H4/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H4&gt;0,ROUND(H4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H4/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J4" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K4" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J4&gt;0,ROUND(J4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J4/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J4&gt;0,ROUND(J4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J4/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L4" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M4" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L4&gt;0,ROUND(L4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L4/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L4&gt;0,ROUND(L4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L4/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N4" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O4" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N4&gt;0,ROUND(N4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N4/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A4,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N4&gt;0,ROUND(N4*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N4/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A4,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P4" s="16">
         <f>'Missed Shifts'!C7</f>
@@ -8315,46 +8472,46 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C5" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B5&gt;0,ROUND(B5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B5/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B5&gt;0,ROUND(B5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B5/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D5" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E5" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D5&gt;0,ROUND(D5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D5/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D5&gt;0,ROUND(D5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D5/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F5" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G5" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F5&gt;0,ROUND(F5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F5/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F5&gt;0,ROUND(F5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F5/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H5" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I5" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H5&gt;0,ROUND(H5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H5/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H5&gt;0,ROUND(H5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H5/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J5" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K5" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J5&gt;0,ROUND(J5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J5/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J5&gt;0,ROUND(J5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J5/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L5" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M5" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L5&gt;0,ROUND(L5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L5/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L5&gt;0,ROUND(L5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L5/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N5" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O5" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N5&gt;0,ROUND(N5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N5/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A5,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N5&gt;0,ROUND(N5*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N5/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A5,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P5" s="16">
         <f>0</f>
@@ -8400,46 +8557,46 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C6" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B6&gt;0,ROUND(B6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B6/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B6&gt;0,ROUND(B6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B6/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D6" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E6" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D6&gt;0,ROUND(D6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D6/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D6&gt;0,ROUND(D6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D6/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F6" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G6" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F6&gt;0,ROUND(F6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F6/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F6&gt;0,ROUND(F6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F6/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H6" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I6" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H6&gt;0,ROUND(H6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H6/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H6&gt;0,ROUND(H6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H6/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J6" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K6" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J6&gt;0,ROUND(J6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J6/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J6&gt;0,ROUND(J6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J6/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L6" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M6" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L6&gt;0,ROUND(L6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L6/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L6&gt;0,ROUND(L6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L6/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N6" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O6" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N6&gt;0,ROUND(N6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N6/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A6,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N6&gt;0,ROUND(N6*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N6/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A6,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P6" s="16">
         <f>'Missed Shifts'!C12</f>
@@ -8485,46 +8642,46 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C7" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B7&gt;0,ROUND(B7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B7/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B7&gt;0,ROUND(B7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B7/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D7" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E7" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D7&gt;0,ROUND(D7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D7/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D7&gt;0,ROUND(D7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D7/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F7" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G7" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F7&gt;0,ROUND(F7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F7/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F7&gt;0,ROUND(F7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F7/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H7" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I7" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H7&gt;0,ROUND(H7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H7/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H7&gt;0,ROUND(H7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H7/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J7" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K7" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J7&gt;0,ROUND(J7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J7/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J7&gt;0,ROUND(J7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J7/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L7" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M7" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L7&gt;0,ROUND(L7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L7/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L7&gt;0,ROUND(L7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L7/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N7" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O7" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N7&gt;0,ROUND(N7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N7/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A7,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N7&gt;0,ROUND(N7*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N7/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A7,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P7" s="16">
         <f>'Missed Shifts'!C15</f>
@@ -8570,46 +8727,46 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C8" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B8&gt;0,ROUND(B8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B8/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B8&gt;0,ROUND(B8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B8/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D8" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E8" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D8&gt;0,ROUND(D8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D8/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D8&gt;0,ROUND(D8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D8/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F8" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G8" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F8&gt;0,ROUND(F8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F8/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F8&gt;0,ROUND(F8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F8/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H8" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I8" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H8&gt;0,ROUND(H8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H8/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H8&gt;0,ROUND(H8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H8/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J8" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K8" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J8&gt;0,ROUND(J8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J8/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J8&gt;0,ROUND(J8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J8/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L8" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M8" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L8&gt;0,ROUND(L8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L8/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L8&gt;0,ROUND(L8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L8/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N8" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O8" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N8&gt;0,ROUND(N8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N8/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A8,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N8&gt;0,ROUND(N8*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N8/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A8,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P8" s="16">
         <f>'Missed Shifts'!C18</f>
@@ -8655,46 +8812,46 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C9" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B9&gt;0,ROUND(B9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B9/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B9&gt;0,ROUND(B9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B9/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D9" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E9" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D9&gt;0,ROUND(D9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D9/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D9&gt;0,ROUND(D9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D9/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F9" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G9" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F9&gt;0,ROUND(F9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F9/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F9&gt;0,ROUND(F9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F9/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H9" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I9" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H9&gt;0,ROUND(H9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H9/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H9&gt;0,ROUND(H9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H9/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J9" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K9" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J9&gt;0,ROUND(J9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J9/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J9&gt;0,ROUND(J9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J9/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L9" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M9" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L9&gt;0,ROUND(L9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L9/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L9&gt;0,ROUND(L9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L9/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N9" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O9" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N9&gt;0,ROUND(N9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N9/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A9,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N9&gt;0,ROUND(N9*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N9/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A9,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P9" s="16">
         <f>0</f>
@@ -8740,46 +8897,46 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C10" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B10&gt;0,ROUND(B10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B10/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B10&gt;0,ROUND(B10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B10/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D10" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E10" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D10&gt;0,ROUND(D10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D10/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D10&gt;0,ROUND(D10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D10/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F10" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G10" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F10&gt;0,ROUND(F10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F10/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F10&gt;0,ROUND(F10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F10/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H10" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I10" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H10&gt;0,ROUND(H10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H10/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H10&gt;0,ROUND(H10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H10/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J10" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K10" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J10&gt;0,ROUND(J10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J10/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J10&gt;0,ROUND(J10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J10/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L10" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M10" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L10&gt;0,ROUND(L10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L10/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L10&gt;0,ROUND(L10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L10/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N10" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O10" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N10&gt;0,ROUND(N10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N10/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A10,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N10&gt;0,ROUND(N10*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N10/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A10,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P10" s="16">
         <f>'Missed Shifts'!C22</f>
@@ -8825,46 +8982,46 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C11" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B11&gt;0,ROUND(B11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B11/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B11&gt;0,ROUND(B11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B11/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D11" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E11" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D11&gt;0,ROUND(D11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D11/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D11&gt;0,ROUND(D11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D11/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F11" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G11" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F11&gt;0,ROUND(F11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F11/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F11&gt;0,ROUND(F11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F11/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H11" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I11" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H11&gt;0,ROUND(H11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H11/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H11&gt;0,ROUND(H11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H11/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J11" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K11" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J11&gt;0,ROUND(J11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J11/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J11&gt;0,ROUND(J11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J11/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L11" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M11" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L11&gt;0,ROUND(L11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L11/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L11&gt;0,ROUND(L11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L11/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N11" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O11" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N11&gt;0,ROUND(N11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N11/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A11,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N11&gt;0,ROUND(N11*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N11/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A11,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P11" s="16">
         <f>'Missed Shifts'!C27</f>
@@ -8906,56 +9063,56 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
+          <t xml:space="preserve">Lebo Lebo</t>
         </is>
       </c>
       <c r="B12" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C12" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B12&gt;0,ROUND(B12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B12/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B12&gt;0,ROUND(B12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B12/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D12" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E12" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D12&gt;0,ROUND(D12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D12/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D12&gt;0,ROUND(D12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D12/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F12" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G12" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F12&gt;0,ROUND(F12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F12/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F12&gt;0,ROUND(F12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F12/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H12" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I12" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H12&gt;0,ROUND(H12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H12/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H12&gt;0,ROUND(H12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H12/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J12" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K12" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J12&gt;0,ROUND(J12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J12/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J12&gt;0,ROUND(J12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J12/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L12" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M12" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L12&gt;0,ROUND(L12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L12/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L12&gt;0,ROUND(L12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L12/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N12" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O12" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N12&gt;0,ROUND(N12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N12/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A12,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N12&gt;0,ROUND(N12*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N12/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A12,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P12" s="16">
-        <f>'Missed Shifts'!C32</f>
+        <f>0</f>
       </c>
       <c r="Q12" s="13">
-        <f>IF('Missed Shifts'!C32=0,IF(P12&gt;0,ROUND(P12*90,2),0),ROUND('Missed Shifts'!D32*P12/'Missed Shifts'!C32,2))</f>
+        <f>IF(P12&gt;0,ROUND(P12*90,2),0)</f>
       </c>
       <c r="R12" s="10">
         <f>SUM(B12,D12,F12,H12,J12,L12,N12,P12)</f>
@@ -8991,62 +9148,62 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharleen Ndlovu</t>
+          <t xml:space="preserve">Patrick Ngozo</t>
         </is>
       </c>
       <c r="B13" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C13" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B13&gt;0,ROUND(B13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B13/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B13&gt;0,ROUND(B13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B13/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D13" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E13" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D13&gt;0,ROUND(D13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D13/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D13&gt;0,ROUND(D13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D13/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F13" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G13" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F13&gt;0,ROUND(F13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F13/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F13&gt;0,ROUND(F13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F13/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H13" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I13" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H13&gt;0,ROUND(H13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H13/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H13&gt;0,ROUND(H13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H13/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J13" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K13" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J13&gt;0,ROUND(J13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J13/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J13&gt;0,ROUND(J13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J13/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L13" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M13" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L13&gt;0,ROUND(L13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L13/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L13&gt;0,ROUND(L13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L13/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N13" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O13" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N13&gt;0,ROUND(N13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N13/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A13,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N13&gt;0,ROUND(N13*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N13/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A13,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P13" s="16">
-        <f>0</f>
+        <f>'Missed Shifts'!C32</f>
       </c>
       <c r="Q13" s="13">
-        <f>IF(P13&gt;0,ROUND(P13*90,2),0)</f>
+        <f>IF('Missed Shifts'!C32=0,IF(P13&gt;0,ROUND(P13*90,2),0),ROUND('Missed Shifts'!D32*P13/'Missed Shifts'!C32,2))</f>
       </c>
       <c r="R13" s="10">
         <f>SUM(B13,D13,F13,H13,J13,L13,N13,P13)</f>
       </c>
       <c r="S13" s="5">
-        <v>3000</v>
+        <f>SUM(C13,E13,G13,I13,K13,M13,O13,Q13)</f>
       </c>
       <c r="T13" s="4">
         <v>0</v>
@@ -9076,62 +9233,62 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon Moyo</t>
+          <t xml:space="preserve">Sharleen Ndlovu</t>
         </is>
       </c>
       <c r="B14" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C14" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B14&gt;0,ROUND(B14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B14/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B14&gt;0,ROUND(B14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B14/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D14" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E14" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D14&gt;0,ROUND(D14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D14/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D14&gt;0,ROUND(D14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D14/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F14" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G14" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F14&gt;0,ROUND(F14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F14/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F14&gt;0,ROUND(F14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F14/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H14" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I14" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H14&gt;0,ROUND(H14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H14/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H14&gt;0,ROUND(H14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H14/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J14" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K14" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J14&gt;0,ROUND(J14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J14/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J14&gt;0,ROUND(J14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J14/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L14" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M14" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L14&gt;0,ROUND(L14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L14/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L14&gt;0,ROUND(L14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L14/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N14" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O14" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N14&gt;0,ROUND(N14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N14/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A14,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N14&gt;0,ROUND(N14*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N14/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A14,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P14" s="16">
-        <f>'Missed Shifts'!C36</f>
+        <f>0</f>
       </c>
       <c r="Q14" s="13">
-        <f>IF('Missed Shifts'!C36=0,IF(P14&gt;0,ROUND(P14*90,2),0),ROUND('Missed Shifts'!D36*P14/'Missed Shifts'!C36,2))</f>
+        <f>IF(P14&gt;0,ROUND(P14*90,2),0)</f>
       </c>
       <c r="R14" s="10">
         <f>SUM(B14,D14,F14,H14,J14,L14,N14,P14)</f>
       </c>
       <c r="S14" s="5">
-        <f>SUM(C14,E14,G14,I14,K14,M14,O14,Q14)</f>
+        <v>3000</v>
       </c>
       <c r="T14" s="4">
         <v>0</v>
@@ -9161,56 +9318,56 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
+          <t xml:space="preserve">Solomon Moyo</t>
         </is>
       </c>
       <c r="B15" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C15" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B15&gt;0,ROUND(B15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B15/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B15&gt;0,ROUND(B15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B15/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D15" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E15" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D15&gt;0,ROUND(D15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D15/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D15&gt;0,ROUND(D15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D15/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F15" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G15" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F15&gt;0,ROUND(F15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F15/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F15&gt;0,ROUND(F15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F15/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H15" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I15" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H15&gt;0,ROUND(H15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H15/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H15&gt;0,ROUND(H15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H15/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J15" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K15" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J15&gt;0,ROUND(J15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J15/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J15&gt;0,ROUND(J15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J15/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L15" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M15" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L15&gt;0,ROUND(L15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L15/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L15&gt;0,ROUND(L15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L15/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N15" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O15" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N15&gt;0,ROUND(N15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N15/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A15,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N15&gt;0,ROUND(N15*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N15/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A15,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P15" s="16">
-        <f>'Missed Shifts'!C39</f>
+        <f>'Missed Shifts'!C36</f>
       </c>
       <c r="Q15" s="13">
-        <f>IF('Missed Shifts'!C39=0,IF(P15&gt;0,ROUND(P15*90,2),0),ROUND('Missed Shifts'!D39*P15/'Missed Shifts'!C39,2))</f>
+        <f>IF('Missed Shifts'!C36=0,IF(P15&gt;0,ROUND(P15*90,2),0),ROUND('Missed Shifts'!D36*P15/'Missed Shifts'!C36,2))</f>
       </c>
       <c r="R15" s="10">
         <f>SUM(B15,D15,F15,H15,J15,L15,N15,P15)</f>
@@ -9246,56 +9403,56 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
       <c r="B16" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C16" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B16&gt;0,ROUND(B16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B16/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B16&gt;0,ROUND(B16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B16/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D16" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E16" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D16&gt;0,ROUND(D16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D16/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D16&gt;0,ROUND(D16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D16/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F16" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G16" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F16&gt;0,ROUND(F16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F16/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F16&gt;0,ROUND(F16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F16/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H16" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I16" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H16&gt;0,ROUND(H16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H16/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H16&gt;0,ROUND(H16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H16/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J16" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K16" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J16&gt;0,ROUND(J16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J16/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J16&gt;0,ROUND(J16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J16/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L16" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M16" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L16&gt;0,ROUND(L16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L16/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L16&gt;0,ROUND(L16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L16/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N16" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O16" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N16&gt;0,ROUND(N16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N16/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A16,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N16&gt;0,ROUND(N16*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N16/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A16,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P16" s="16">
-        <f>0</f>
+        <f>'Missed Shifts'!C39</f>
       </c>
       <c r="Q16" s="13">
-        <f>IF(P16&gt;0,ROUND(P16*90,2),0)</f>
+        <f>IF('Missed Shifts'!C39=0,IF(P16&gt;0,ROUND(P16*90,2),0),ROUND('Missed Shifts'!D39*P16/'Missed Shifts'!C39,2))</f>
       </c>
       <c r="R16" s="10">
         <f>SUM(B16,D16,F16,H16,J16,L16,N16,P16)</f>
@@ -9331,56 +9488,56 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thina Dyani</t>
+          <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
       <c r="B17" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C17" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B17&gt;0,ROUND(B17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B17/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B17&gt;0,ROUND(B17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B17/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D17" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E17" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D17&gt;0,ROUND(D17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D17/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D17&gt;0,ROUND(D17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D17/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F17" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G17" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F17&gt;0,ROUND(F17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F17/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F17&gt;0,ROUND(F17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F17/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H17" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I17" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H17&gt;0,ROUND(H17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H17/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H17&gt;0,ROUND(H17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H17/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J17" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K17" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J17&gt;0,ROUND(J17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J17/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J17&gt;0,ROUND(J17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J17/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L17" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M17" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L17&gt;0,ROUND(L17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L17/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L17&gt;0,ROUND(L17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L17/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N17" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O17" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N17&gt;0,ROUND(N17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N17/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A17,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N17&gt;0,ROUND(N17*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N17/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A17,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P17" s="16">
-        <f>'Missed Shifts'!C42</f>
+        <f>0</f>
       </c>
       <c r="Q17" s="13">
-        <f>IF('Missed Shifts'!C42=0,IF(P17&gt;0,ROUND(P17*90,2),0),ROUND('Missed Shifts'!D42*P17/'Missed Shifts'!C42,2))</f>
+        <f>IF(P17&gt;0,ROUND(P17*90,2),0)</f>
       </c>
       <c r="R17" s="10">
         <f>SUM(B17,D17,F17,H17,J17,L17,N17,P17)</f>
@@ -9416,56 +9573,56 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+          <t xml:space="preserve">Thina Dyani</t>
         </is>
       </c>
       <c r="B18" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="C18" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(B18&gt;0,ROUND(B18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,"")*B18/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,B$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B18&gt;0,ROUND(B18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B18/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="D18" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="E18" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(D18&gt;0,ROUND(D18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,"")*D18/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,D$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D18&gt;0,ROUND(D18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D18/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="F18" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="G18" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(F18&gt;0,ROUND(F18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,"")*F18/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,F$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F18&gt;0,ROUND(F18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F18/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="H18" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="I18" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(H18&gt;0,ROUND(H18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,"")*H18/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,H$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H18&gt;0,ROUND(H18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H18/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="J18" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="K18" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(J18&gt;0,ROUND(J18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,"")*J18/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,J$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J18&gt;0,ROUND(J18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J18/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="L18" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="M18" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(L18&gt;0,ROUND(L18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,"")*L18/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,L$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L18&gt;0,ROUND(L18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L18/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="N18" s="16">
-        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")</f>
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
       </c>
       <c r="O18" s="4">
-        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")=0,IF(N18&gt;0,ROUND(N18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,"")*N18/SUMIFS('Wage Detail Linked'!$O$5:$O$95,'Wage Detail Linked'!$B$5:$B$95,$A18,'Wage Detail Linked'!$C$5:$C$95,N$2,'Wage Detail Linked'!$E$5:$E$95,""),2))</f>
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N18&gt;0,ROUND(N18*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N18/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A18,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
       </c>
       <c r="P18" s="16">
-        <f>0</f>
+        <f>'Missed Shifts'!C42</f>
       </c>
       <c r="Q18" s="13">
-        <f>IF(P18&gt;0,ROUND(P18*90,2),0)</f>
+        <f>IF('Missed Shifts'!C42=0,IF(P18&gt;0,ROUND(P18*90,2),0),ROUND('Missed Shifts'!D42*P18/'Missed Shifts'!C42,2))</f>
       </c>
       <c r="R18" s="10">
         <f>SUM(B18,D18,F18,H18,J18,L18,N18,P18)</f>
@@ -9501,86 +9658,171 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+        </is>
+      </c>
+      <c r="B19" s="16">
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
+      </c>
+      <c r="C19" s="4">
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(B19&gt;0,ROUND(B19*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,"")*B19/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,B$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
+      </c>
+      <c r="D19" s="16">
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
+      </c>
+      <c r="E19" s="4">
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(D19&gt;0,ROUND(D19*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,"")*D19/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,D$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
+      </c>
+      <c r="F19" s="16">
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
+      </c>
+      <c r="G19" s="4">
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(F19&gt;0,ROUND(F19*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,"")*F19/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,F$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
+      </c>
+      <c r="H19" s="16">
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
+      </c>
+      <c r="I19" s="4">
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(H19&gt;0,ROUND(H19*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,"")*H19/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,H$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
+      </c>
+      <c r="J19" s="16">
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
+      </c>
+      <c r="K19" s="4">
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(J19&gt;0,ROUND(J19*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,"")*J19/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,J$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
+      </c>
+      <c r="L19" s="16">
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
+      </c>
+      <c r="M19" s="4">
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(L19&gt;0,ROUND(L19*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,"")*L19/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,L$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
+      </c>
+      <c r="N19" s="16">
+        <f>SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")</f>
+      </c>
+      <c r="O19" s="4">
+        <f>IF(SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")=0,IF(N19&gt;0,ROUND(N19*90,2),0),ROUND(SUMIFS('Wage Detail Linked'!$R$5:$R$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,"")*N19/SUMIFS('Wage Detail Linked'!$O$5:$O$97,'Wage Detail Linked'!$B$5:$B$97,$A19,'Wage Detail Linked'!$C$5:$C$97,N$2,'Wage Detail Linked'!$E$5:$E$97,""),2))</f>
+      </c>
+      <c r="P19" s="16">
+        <f>0</f>
+      </c>
+      <c r="Q19" s="13">
+        <f>IF(P19&gt;0,ROUND(P19*90,2),0)</f>
+      </c>
+      <c r="R19" s="10">
+        <f>SUM(B19,D19,F19,H19,J19,L19,N19,P19)</f>
+      </c>
+      <c r="S19" s="5">
+        <f>SUM(C19,E19,G19,I19,K19,M19,O19,Q19)</f>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="7">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <f>MAX(0,T19-U19)</f>
+      </c>
+      <c r="W19" s="4">
+        <v>0</v>
+      </c>
+      <c r="X19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4">
+        <f>MAX(0,0-X19)</f>
+      </c>
+      <c r="Z19" s="4">
+        <f>U19+X19</f>
+      </c>
+      <c r="AA19" s="13">
+        <f>MAX(0,S19-Z19)</f>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="10">
-        <f>SUM(B4:B18)</f>
-      </c>
-      <c r="C19" s="5">
-        <f>SUM(C4:C18)</f>
-      </c>
-      <c r="D19" s="10">
-        <f>SUM(D4:D18)</f>
-      </c>
-      <c r="E19" s="5">
-        <f>SUM(E4:E18)</f>
-      </c>
-      <c r="F19" s="10">
-        <f>SUM(F4:F18)</f>
-      </c>
-      <c r="G19" s="5">
-        <f>SUM(G4:G18)</f>
-      </c>
-      <c r="H19" s="10">
-        <f>SUM(H4:H18)</f>
-      </c>
-      <c r="I19" s="5">
-        <f>SUM(I4:I18)</f>
-      </c>
-      <c r="J19" s="10">
-        <f>SUM(J4:J18)</f>
-      </c>
-      <c r="K19" s="5">
-        <f>SUM(K4:K18)</f>
-      </c>
-      <c r="L19" s="10">
-        <f>SUM(L4:L18)</f>
-      </c>
-      <c r="M19" s="5">
-        <f>SUM(M4:M18)</f>
-      </c>
-      <c r="N19" s="10">
-        <f>SUM(N4:N18)</f>
-      </c>
-      <c r="O19" s="5">
-        <f>SUM(O4:O18)</f>
-      </c>
-      <c r="P19" s="10">
-        <f>SUM(P4:P18)</f>
-      </c>
-      <c r="Q19" s="5">
-        <f>SUM(Q4:Q18)</f>
-      </c>
-      <c r="R19" s="10">
-        <f>SUM(R4:R18)</f>
-      </c>
-      <c r="S19" s="5">
-        <f>SUM(S4:S18)</f>
-      </c>
-      <c r="T19" s="5">
-        <f>SUM(T4:T18)</f>
-      </c>
-      <c r="U19" s="5">
-        <f>SUM(U4:U18)</f>
-      </c>
-      <c r="V19" s="5">
-        <f>SUM(V4:V18)</f>
-      </c>
-      <c r="W19" s="5">
-        <f>SUM(W4:W18)</f>
-      </c>
-      <c r="X19" s="5">
-        <f>SUM(X4:X18)</f>
-      </c>
-      <c r="Y19" s="5">
-        <f>SUM(Y4:Y18)</f>
-      </c>
-      <c r="Z19" s="5">
-        <f>SUM(Z4:Z18)</f>
-      </c>
-      <c r="AA19" s="5">
-        <f>SUM(AA4:AA18)</f>
+      <c r="B20" s="10">
+        <f>SUM(B4:B19)</f>
+      </c>
+      <c r="C20" s="5">
+        <f>SUM(C4:C19)</f>
+      </c>
+      <c r="D20" s="10">
+        <f>SUM(D4:D19)</f>
+      </c>
+      <c r="E20" s="5">
+        <f>SUM(E4:E19)</f>
+      </c>
+      <c r="F20" s="10">
+        <f>SUM(F4:F19)</f>
+      </c>
+      <c r="G20" s="5">
+        <f>SUM(G4:G19)</f>
+      </c>
+      <c r="H20" s="10">
+        <f>SUM(H4:H19)</f>
+      </c>
+      <c r="I20" s="5">
+        <f>SUM(I4:I19)</f>
+      </c>
+      <c r="J20" s="10">
+        <f>SUM(J4:J19)</f>
+      </c>
+      <c r="K20" s="5">
+        <f>SUM(K4:K19)</f>
+      </c>
+      <c r="L20" s="10">
+        <f>SUM(L4:L19)</f>
+      </c>
+      <c r="M20" s="5">
+        <f>SUM(M4:M19)</f>
+      </c>
+      <c r="N20" s="10">
+        <f>SUM(N4:N19)</f>
+      </c>
+      <c r="O20" s="5">
+        <f>SUM(O4:O19)</f>
+      </c>
+      <c r="P20" s="10">
+        <f>SUM(P4:P19)</f>
+      </c>
+      <c r="Q20" s="5">
+        <f>SUM(Q4:Q19)</f>
+      </c>
+      <c r="R20" s="10">
+        <f>SUM(R4:R19)</f>
+      </c>
+      <c r="S20" s="5">
+        <f>SUM(S4:S19)</f>
+      </c>
+      <c r="T20" s="5">
+        <f>SUM(T4:T19)</f>
+      </c>
+      <c r="U20" s="5">
+        <f>SUM(U4:U19)</f>
+      </c>
+      <c r="V20" s="5">
+        <f>SUM(V4:V19)</f>
+      </c>
+      <c r="W20" s="5">
+        <f>SUM(W4:W19)</f>
+      </c>
+      <c r="X20" s="5">
+        <f>SUM(X4:X19)</f>
+      </c>
+      <c r="Y20" s="5">
+        <f>SUM(Y4:Y19)</f>
+      </c>
+      <c r="Z20" s="5">
+        <f>SUM(Z4:Z19)</f>
+      </c>
+      <c r="AA20" s="5">
+        <f>SUM(AA4:AA19)</f>
       </c>
     </row>
   </sheetData>
@@ -10062,7 +10304,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
+          <t xml:space="preserve">Lebo Lebo</t>
         </is>
       </c>
       <c r="B13" s="9">
@@ -10105,7 +10347,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharleen Ndlovu</t>
+          <t xml:space="preserve">Patrick Ngozo</t>
         </is>
       </c>
       <c r="B14" s="9">
@@ -10148,7 +10390,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon Moyo</t>
+          <t xml:space="preserve">Sharleen Ndlovu</t>
         </is>
       </c>
       <c r="B15" s="9">
@@ -10191,7 +10433,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
+          <t xml:space="preserve">Solomon Moyo</t>
         </is>
       </c>
       <c r="B16" s="9">
@@ -10234,7 +10476,7 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
       <c r="B17" s="9">
@@ -10277,7 +10519,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thina Dyani</t>
+          <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
       <c r="B18" s="9">
@@ -10320,7 +10562,7 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+          <t xml:space="preserve">Thina Dyani</t>
         </is>
       </c>
       <c r="B19" s="9">
@@ -10361,46 +10603,89 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>--('Auditor Trail Linked'!B19&gt;0)+--('Auditor Trail Linked'!D19&gt;0)+--('Auditor Trail Linked'!F19&gt;0)+--('Auditor Trail Linked'!H19&gt;0)+--('Auditor Trail Linked'!J19&gt;0)+--('Auditor Trail Linked'!L19&gt;0)+--('Auditor Trail Linked'!N19&gt;0)</f>
+      </c>
+      <c r="C20" s="9">
+        <f>'Auditor Trail Linked'!R19</f>
+      </c>
+      <c r="D20" s="9">
+        <f>'Auditor Trail Linked'!P19</f>
+      </c>
+      <c r="E20" s="4">
+        <f>'Auditor Trail Linked'!S19</f>
+      </c>
+      <c r="F20" s="4">
+        <f>'Auditor Trail Linked'!T19</f>
+      </c>
+      <c r="G20" s="4">
+        <f>'Auditor Trail Linked'!U19</f>
+      </c>
+      <c r="H20" s="4">
+        <f>'Auditor Trail Linked'!V19</f>
+      </c>
+      <c r="I20" s="4">
+        <f>'Auditor Trail Linked'!W19</f>
+      </c>
+      <c r="J20" s="4">
+        <f>'Auditor Trail Linked'!X19</f>
+      </c>
+      <c r="K20" s="4">
+        <f>'Auditor Trail Linked'!Y19</f>
+      </c>
+      <c r="L20" s="4">
+        <f>'Auditor Trail Linked'!Z19</f>
+      </c>
+      <c r="M20" s="13">
+        <f>'Auditor Trail Linked'!AA19</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="10">
-        <f>SUM(B5:B19)</f>
-      </c>
-      <c r="C20" s="10">
-        <f>SUM(C5:C19)</f>
-      </c>
-      <c r="D20" s="10">
-        <f>SUM(D5:D19)</f>
-      </c>
-      <c r="E20" s="5">
-        <f>SUM(E5:E19)</f>
-      </c>
-      <c r="F20" s="5">
-        <f>SUM(F5:F19)</f>
-      </c>
-      <c r="G20" s="5">
-        <f>SUM(G5:G19)</f>
-      </c>
-      <c r="H20" s="5">
-        <f>SUM(H5:H19)</f>
-      </c>
-      <c r="I20" s="5">
-        <f>SUM(I5:I19)</f>
-      </c>
-      <c r="J20" s="5">
-        <f>SUM(J5:J19)</f>
-      </c>
-      <c r="K20" s="5">
-        <f>SUM(K5:K19)</f>
-      </c>
-      <c r="L20" s="5">
-        <f>SUM(L5:L19)</f>
-      </c>
-      <c r="M20" s="5">
-        <f>SUM(M5:M19)</f>
+      <c r="B21" s="10">
+        <f>SUM(B5:B20)</f>
+      </c>
+      <c r="C21" s="10">
+        <f>SUM(C5:C20)</f>
+      </c>
+      <c r="D21" s="10">
+        <f>SUM(D5:D20)</f>
+      </c>
+      <c r="E21" s="5">
+        <f>SUM(E5:E20)</f>
+      </c>
+      <c r="F21" s="5">
+        <f>SUM(F5:F20)</f>
+      </c>
+      <c r="G21" s="5">
+        <f>SUM(G5:G20)</f>
+      </c>
+      <c r="H21" s="5">
+        <f>SUM(H5:H20)</f>
+      </c>
+      <c r="I21" s="5">
+        <f>SUM(I5:I20)</f>
+      </c>
+      <c r="J21" s="5">
+        <f>SUM(J5:J20)</f>
+      </c>
+      <c r="K21" s="5">
+        <f>SUM(K5:K20)</f>
+      </c>
+      <c r="L21" s="5">
+        <f>SUM(L5:L20)</f>
+      </c>
+      <c r="M21" s="5">
+        <f>SUM(M5:M20)</f>
       </c>
     </row>
   </sheetData>
@@ -13031,36 +13316,36 @@
         </is>
       </c>
       <c r="B46" s="23">
-        <v>9954</v>
+        <v>10149</v>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
+          <t xml:space="preserve">Lebo Lebo</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:30–16:00 Wearhouse</t>
+          <t xml:space="preserve">07:00–13:25 Warehouse</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Venue/Event</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">The wording says Wearhouse — Loading but the work type is Normal. Choose Warehouse (R81,25/h, 9.5 h less 0.5 h staff meeting = R731,25) or Venue/Event (R95/h = R902,50). The shift stays at R795 until you choose.</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H46" s="23"/>
       <c r="I46" s="24">
-        <v>9.5</v>
+        <v>6.42</v>
       </c>
       <c r="J46" s="23"/>
       <c r="K46" s="23" t="inlineStr">
@@ -13075,74 +13360,72 @@
       </c>
       <c r="M46" s="23" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-25 07:18:01</t>
+        </is>
+      </c>
+      <c r="N46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Event/Venue rate chosen — shift #9861 R802,50 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Venue/event public holiday (Heritage Day): 6.42 h × R190 (R95 × 2) = R1 219,17; R0 until approved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B47" s="26">
+        <v>9954</v>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrick Ngozo</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–16:00 Wearhouse</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Venue/Event</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The wording says Wearhouse — Loading but the work type is Normal. Choose Warehouse (R81,25/h, 9.5 h less 0.5 h staff meeting = R731,25) or Venue/Event (R95/h = R902,50). The shift stays at R795 until you choose.</t>
+        </is>
+      </c>
+      <c r="H47" s="26"/>
+      <c r="I47" s="27">
+        <v>9.5</v>
+      </c>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M47" s="26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-22 12:28:15</t>
         </is>
       </c>
-      <c r="N46" s="23" t="inlineStr">
+      <c r="N47" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Warehouse rate chosen — shift #9773 R795,00 → R731,25 (Warehouse: 9.5 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 9 h × R81,25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B47" s="23">
-        <v>10143</v>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patrick Ngozo</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06:30–15:00 Wearhouse</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Patrick Ngozo worked 06:30–15:00. Held for owner approval.</t>
-        </is>
-      </c>
-      <c r="H47" s="23"/>
-      <c r="I47" s="24">
-        <v>8.5</v>
-      </c>
-      <c r="J47" s="24">
-        <v>8</v>
-      </c>
-      <c r="K47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:30:29</t>
-        </is>
-      </c>
-      <c r="N47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day), owner set hours 06:30–15:00: 8.5 h − 0.5 h staff meeting = 8 h × R162,50 = R1 300,00</t>
         </is>
       </c>
     </row>
@@ -13153,118 +13436,118 @@
         </is>
       </c>
       <c r="B48" s="26">
-        <v>10063</v>
+        <v>10143</v>
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon Moyo</t>
+          <t xml:space="preserve">Patrick Ngozo</t>
         </is>
       </c>
       <c r="D48" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+          <t xml:space="preserve">06:30–15:00 Wearhouse</t>
         </is>
       </c>
       <c r="F48" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G48" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Patrick Ngozo worked 06:30–15:00. Held for owner approval.</t>
         </is>
       </c>
       <c r="H48" s="26"/>
       <c r="I48" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="J48" s="27">
+        <v>8</v>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 10:30:29</t>
+        </is>
+      </c>
+      <c r="N48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep at the holiday rate: Warehouse public holiday (Heritage Day), owner set hours 06:30–15:00: 8.5 h − 0.5 h staff meeting = 8 h × R162,50 = R1 300,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B49" s="29">
+        <v>10063</v>
+      </c>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solomon Moyo</t>
+        </is>
+      </c>
+      <c r="D49" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+      <c r="E49" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
+        </is>
+      </c>
+      <c r="F49" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+        </is>
+      </c>
+      <c r="G49" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H49" s="29"/>
+      <c r="I49" s="30">
         <v>9</v>
       </c>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26" t="inlineStr">
+      <c r="J49" s="29"/>
+      <c r="K49" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L48" s="26" t="inlineStr">
+      <c r="L49" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M48" s="26" t="inlineStr">
+      <c r="M49" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 10:48:16</t>
         </is>
       </c>
-      <c r="N48" s="26" t="inlineStr">
+      <c r="N49" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Warehouse rate chosen — shift #9835 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B49" s="26">
-        <v>10060</v>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solomon Moyo</t>
-        </is>
-      </c>
-      <c r="D49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
-      <c r="E49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–15:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
-        </is>
-      </c>
-      <c r="G49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Solomon Moyo worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Botanical Gardens (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
-        </is>
-      </c>
-      <c r="H49" s="26"/>
-      <c r="I49" s="27">
-        <v>8</v>
-      </c>
-      <c r="J49" s="27">
-        <v>7.5</v>
-      </c>
-      <c r="K49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve adjusted</t>
-        </is>
-      </c>
-      <c r="L49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 10:31:21</t>
-        </is>
-      </c>
-      <c r="N49" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — warehouse, hours set to 07:00–15:00 (worker wrote Botanical Gardens until 16:00): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1 218,75</t>
         </is>
       </c>
     </row>
@@ -13275,300 +13558,302 @@
         </is>
       </c>
       <c r="B50" s="29">
-        <v>10074</v>
+        <v>10060</v>
       </c>
       <c r="C50" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
+          <t xml:space="preserve">Solomon Moyo</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:00–18:00 FNB</t>
+          <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warehouse claimed — but the entry names “Johannesburg”</t>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAREHOUSE CLAIMED BUT THE ENTRY NAMES “Johannesburg”: Takavaudza Chokuda selected Warehouse Team at “FNB” for 2.00 h on Thu 17 Sep 2026, but wrote “Johannesburg” — that is a venue, not the warehouse. 6 workers were at a venue that day (Additional 5 hour shift - 17/09/2026 Parys Golf Day, Botanical garden Pretoria, FNB Stadium, Parys golf &amp; country Estate, Parys Country Club, Parys, Botanical gardens, Fnb stadium). If he was at “Johannesburg”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Solomon Moyo worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Botanical Gardens (Normal). Public-holiday work is not paid automatically. Recommended: Venue/event public holiday (Heritage Day): 9 h × R190 (R95 × 2) = R1 710,00. R0 is paid until the owner approves or declines.</t>
         </is>
       </c>
       <c r="H50" s="29"/>
       <c r="I50" s="30">
+        <v>8</v>
+      </c>
+      <c r="J50" s="30">
+        <v>7.5</v>
+      </c>
+      <c r="K50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve adjusted</t>
+        </is>
+      </c>
+      <c r="L50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 10:31:21</t>
+        </is>
+      </c>
+      <c r="N50" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — warehouse, hours set to 07:00–15:00 (worker wrote Botanical Gardens until 16:00): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1 218,75</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B51" s="32">
+        <v>10074</v>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="E51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–18:00 FNB</t>
+        </is>
+      </c>
+      <c r="F51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse claimed — but the entry names “Johannesburg”</t>
+        </is>
+      </c>
+      <c r="G51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAREHOUSE CLAIMED BUT THE ENTRY NAMES “Johannesburg”: Takavaudza Chokuda selected Warehouse Team at “FNB” for 2.00 h on Thu 17 Sep 2026, but wrote “Johannesburg” — that is a venue, not the warehouse. 6 workers were at a venue that day (Additional 5 hour shift - 17/09/2026 Parys Golf Day, Botanical garden Pretoria, FNB Stadium, Parys golf &amp; country Estate, Parys Country Club, Parys, Botanical gardens, Fnb stadium). If he was at “Johannesburg”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
+        </is>
+      </c>
+      <c r="H51" s="32"/>
+      <c r="I51" s="33">
         <v>2</v>
       </c>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29" t="inlineStr">
+      <c r="J51" s="32"/>
+      <c r="K51" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L50" s="29" t="inlineStr">
+      <c r="L51" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M50" s="29" t="inlineStr">
+      <c r="M51" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 11:01:57</t>
         </is>
       </c>
-      <c r="N50" s="29" t="inlineStr">
+      <c r="N51" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Event/Venue rate chosen — shift #9815 R162,50 → R190,00 (Venue/event: 2 h × R95)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B51" s="29">
+      <c r="B52" s="32">
         <v>9955</v>
       </c>
-      <c r="C51" s="29" t="inlineStr">
+      <c r="C52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
-      <c r="E51" s="29" t="inlineStr">
+      <c r="E52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Crew pattern — 8 of 9 at a venue, this one says Warehouse</t>
         </is>
       </c>
-      <c r="G51" s="29" t="inlineStr">
+      <c r="G52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">CREW PATTERN: 8 of 9 workers were at a venue on Mon 21 Sep 2026 (FNB Stadium, FNB strike down, Fnb stadium) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
         </is>
       </c>
-      <c r="H51" s="29"/>
-      <c r="I51" s="30">
+      <c r="H52" s="32"/>
+      <c r="I52" s="33">
         <v>9</v>
       </c>
-      <c r="J51" s="30">
+      <c r="J52" s="33">
         <v>9</v>
       </c>
-      <c r="K51" s="29" t="inlineStr">
+      <c r="K52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L51" s="29" t="inlineStr">
+      <c r="L52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M51" s="29" t="inlineStr">
+      <c r="M52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 11:01:58</t>
         </is>
       </c>
-      <c r="N51" s="29" t="inlineStr">
+      <c r="N52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">WAREHOUSE — R81,25/h chosen by Bernie Burness for draft #830 — will pay R690,63 when final-submitted (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B52" s="29">
+      <c r="B53" s="32">
         <v>10075</v>
       </c>
-      <c r="C52" s="29" t="inlineStr">
+      <c r="C53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
-      <c r="D52" s="29" t="inlineStr">
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
-      <c r="E52" s="29" t="inlineStr">
+      <c r="E53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–16:00 Riverside</t>
         </is>
       </c>
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Warehouse claimed — but the entry names “The vaal”</t>
         </is>
       </c>
-      <c r="G52" s="29" t="inlineStr">
+      <c r="G53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">WAREHOUSE CLAIMED BUT THE ENTRY NAMES “The vaal”: Takavaudza Chokuda selected Warehouse Team at “Riverside” for 9.00 h on Wed 23 Sep 2026, but wrote “The vaal” — that is a venue, not the warehouse. 6 workers were at a venue that day (Work with the Team, wharehouse, Set up vaal Boating, Riverside sun, Vaal Boating Season, Stone Haven And Riverside Sun). If he was at “The vaal”, he is due the venue rate (R95/h); if he was really in the warehouse, R81,25/h. Choose below.</t>
         </is>
       </c>
-      <c r="H52" s="29"/>
-      <c r="I52" s="30">
+      <c r="H53" s="32"/>
+      <c r="I53" s="33">
         <v>9</v>
       </c>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29" t="inlineStr">
+      <c r="J53" s="32"/>
+      <c r="K53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L52" s="29" t="inlineStr">
+      <c r="L53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M52" s="29" t="inlineStr">
+      <c r="M53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 11:01:57</t>
         </is>
       </c>
-      <c r="N52" s="29" t="inlineStr">
+      <c r="N53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Event/Venue rate chosen — shift #9819 R690,63 → R855,00 (Venue/event: 9 h × R95)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B53" s="29">
+      <c r="B54" s="32">
         <v>10039</v>
       </c>
-      <c r="C53" s="29" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
-      <c r="E53" s="29" t="inlineStr">
+      <c r="E54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
-      <c r="F53" s="29" t="inlineStr">
+      <c r="F54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
-      <c r="G53" s="29" t="inlineStr">
+      <c r="G54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Takavaudza Chokuda worked 07:00–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Warehouse Team). Public-holiday work is not paid automatically. Recommended: Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50. R0 is paid until the owner approves or declines.</t>
         </is>
       </c>
-      <c r="H53" s="29"/>
-      <c r="I53" s="30">
+      <c r="H54" s="32"/>
+      <c r="I54" s="33">
         <v>8</v>
       </c>
-      <c r="J53" s="30">
+      <c r="J54" s="33">
         <v>7.5</v>
       </c>
-      <c r="K53" s="29" t="inlineStr">
+      <c r="K54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
-      <c r="L53" s="29" t="inlineStr">
+      <c r="L54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M53" s="29" t="inlineStr">
+      <c r="M54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 10:32:07</t>
         </is>
       </c>
-      <c r="N53" s="29" t="inlineStr">
+      <c r="N54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B54" s="29">
-        <v>10076</v>
-      </c>
-      <c r="C54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Takavaudza Chokuda</t>
-        </is>
-      </c>
-      <c r="D54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-25</t>
-        </is>
-      </c>
-      <c r="E54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crew pattern — 7 of 8 at a venue, this one says Warehouse</t>
-        </is>
-      </c>
-      <c r="G54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CREW PATTERN: 7 of 8 workers were at a venue on Fri 25 Sep 2026 (The Capital Sandton and Bonitical Emmarentia, Pretoria country club, Botanical, Vaal Boating, Riverside sun, Pretoria Country Club, Capital hotel / botanical gardens JHB) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
-        </is>
-      </c>
-      <c r="H54" s="29"/>
-      <c r="I54" s="30">
-        <v>9</v>
-      </c>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 11:01:58</t>
-        </is>
-      </c>
-      <c r="N54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9817 R690,63 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -13579,31 +13864,31 @@
         </is>
       </c>
       <c r="B55" s="32">
-        <v>10080</v>
+        <v>10076</v>
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
+          <t xml:space="preserve">Takavaudza Chokuda</t>
         </is>
       </c>
       <c r="D55" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="E55" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">07:00–16:00 FNB Stadium and Warehouse</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F55" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+          <t xml:space="preserve">Crew pattern — 7 of 8 at a venue, this one says Warehouse</t>
         </is>
       </c>
       <c r="G55" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+          <t xml:space="preserve">CREW PATTERN: 7 of 8 workers were at a venue on Fri 25 Sep 2026 (The Capital Sandton and Bonitical Emmarentia, Pretoria country club, Botanical, Vaal Boating, Riverside sun, Pretoria Country Club, Capital hotel / botanical gardens JHB) — Takavaudza Chokuda says Warehouse for 9.00 h. Check he was not at the venue (R95/h would be due).</t>
         </is>
       </c>
       <c r="H55" s="32"/>
@@ -13623,254 +13908,254 @@
       </c>
       <c r="M55" s="32" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-23 11:01:58</t>
+        </is>
+      </c>
+      <c r="N55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9817 R690,63 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B56" s="17">
+        <v>10080</v>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thandanani Nkala</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-21</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–16:00 FNB Stadium and Warehouse</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
+        </is>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="18">
+        <v>9</v>
+      </c>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-23 09:24:21</t>
         </is>
       </c>
-      <c r="N55" s="32" t="inlineStr">
+      <c r="N56" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Event/Venue rate chosen — shift #9840 R750,00 → R855,00 (Venue/event: 9 h × R95)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="32" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B56" s="32">
+      <c r="B57" s="17">
         <v>10087</v>
       </c>
-      <c r="C56" s="32" t="inlineStr">
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
-      <c r="E56" s="32" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
-      <c r="F56" s="32" t="inlineStr">
+      <c r="F57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
-      <c r="G56" s="32" t="inlineStr">
+      <c r="G57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
-      <c r="H56" s="32"/>
-      <c r="I56" s="33">
+      <c r="H57" s="17"/>
+      <c r="I57" s="18">
         <v>9</v>
       </c>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32" t="inlineStr">
+      <c r="J57" s="17"/>
+      <c r="K57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L56" s="32" t="inlineStr">
+      <c r="L57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M56" s="32" t="inlineStr">
+      <c r="M57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 09:24:24</t>
         </is>
       </c>
-      <c r="N56" s="32" t="inlineStr">
+      <c r="N57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Warehouse rate chosen — shift #9844 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="32" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B57" s="32">
+      <c r="B58" s="17">
         <v>10084</v>
       </c>
-      <c r="C57" s="32" t="inlineStr">
+      <c r="C58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
-      <c r="E57" s="32" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
-      <c r="F57" s="32" t="inlineStr">
+      <c r="F58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
-      <c r="G57" s="32" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
-      <c r="H57" s="32"/>
-      <c r="I57" s="33">
+      <c r="H58" s="17"/>
+      <c r="I58" s="18">
         <v>8</v>
       </c>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32" t="inlineStr">
+      <c r="J58" s="17"/>
+      <c r="K58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">approve original</t>
         </is>
       </c>
-      <c r="L57" s="32" t="inlineStr">
+      <c r="L58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M57" s="32" t="inlineStr">
+      <c r="M58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 09:24:33</t>
         </is>
       </c>
-      <c r="N57" s="32" t="inlineStr">
+      <c r="N58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Warehouse rate chosen — shift #9842 R1 620,00 → R0,00 (PUBLIC HOLIDAY — HELD for owner approval — recommended Warehouse public holiday (Heritage Day): 9 h × R162,50 (R81,25 × 2, no meeting deduction) = R1 462,50; R0 until approved)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="32" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">RESOLVED</t>
         </is>
       </c>
-      <c r="B58" s="32">
+      <c r="B59" s="17">
         <v>10142</v>
       </c>
-      <c r="C58" s="32" t="inlineStr">
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
-      <c r="D58" s="32" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
-      <c r="E58" s="32" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">07:00–15:00 Warehouse</t>
         </is>
       </c>
-      <c r="F58" s="32" t="inlineStr">
+      <c r="F59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
         </is>
       </c>
-      <c r="G58" s="32" t="inlineStr">
+      <c r="G59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">PUBLIC HOLIDAY — Heritage Day (24 Sep 2026): Thandanani Nkala worked 07:00–15:00. Held for owner approval.</t>
         </is>
       </c>
-      <c r="H58" s="32"/>
-      <c r="I58" s="33">
+      <c r="H59" s="17"/>
+      <c r="I59" s="18">
         <v>8</v>
       </c>
-      <c r="J58" s="33">
+      <c r="J59" s="18">
         <v>7.5</v>
       </c>
-      <c r="K58" s="32" t="inlineStr">
+      <c r="K59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
-      <c r="L58" s="32" t="inlineStr">
+      <c r="L59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M58" s="32" t="inlineStr">
+      <c r="M59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 10:32:12</t>
         </is>
       </c>
-      <c r="N58" s="32" t="inlineStr">
+      <c r="N59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 07:00–15:00 (no set-ups): Warehouse public holiday (Heritage Day), owner set hours 07:00–15:00: 8.0 h − 0.5 h staff meeting 07:00–07:30 (unpaid) = 7.5 h × R162,50 (R81,25 × 2) = R1218.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESOLVED</t>
-        </is>
-      </c>
-      <c r="B59" s="32">
-        <v>10082</v>
-      </c>
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thandanani Nkala</t>
-        </is>
-      </c>
-      <c r="D59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-25</t>
-        </is>
-      </c>
-      <c r="E59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07:00–16:00 Warehouse</t>
-        </is>
-      </c>
-      <c r="F59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
-        </is>
-      </c>
-      <c r="G59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
-        </is>
-      </c>
-      <c r="H59" s="32"/>
-      <c r="I59" s="33">
-        <v>9</v>
-      </c>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approve original</t>
-        </is>
-      </c>
-      <c r="L59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bernie Burness</t>
-        </is>
-      </c>
-      <c r="M59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-23 09:24:36</t>
-        </is>
-      </c>
-      <c r="N59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warehouse rate chosen — shift #9841 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
         </is>
       </c>
     </row>
@@ -13881,56 +14166,116 @@
         </is>
       </c>
       <c r="B60" s="17">
-        <v>10033</v>
+        <v>10082</v>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+          <t xml:space="preserve">Thandanani Nkala</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">06:30–14:00 Warehouse</t>
+          <t xml:space="preserve">07:00–16:00 Warehouse</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
+          <t xml:space="preserve">Rate choice: Warehouse or Event/Venue</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Tsotlego Petrus Malakoane worked 06:30–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Normal). Public-holiday work is not paid automatically. Recommended: Petrus public holiday (Heritage Day): no fixed day — 9.5 h × R160 (R80 × 2) = R1 520,00. R0 is paid until the owner approves or declines.</t>
+          <t xml:space="preserve">RATE CHOICE NEEDED: the wording mentions "warehouse" but the work type is Normal, so it is not clearly warehouse-only. Bernie must choose Warehouse (R81,25/h, Sunday R97,50, meeting time unpaid) or Venue/Event (R95/h, Sunday R114) before the rate is decided. Until then the shift stays at the engine amount.</t>
         </is>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="18">
+        <v>9</v>
+      </c>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">approve original</t>
+        </is>
+      </c>
+      <c r="L60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernie Burness</t>
+        </is>
+      </c>
+      <c r="M60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 09:24:36</t>
+        </is>
+      </c>
+      <c r="N60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse rate chosen — shift #9841 R750,00 → R690,63 (Warehouse: 9 h − 0.5 h staff meeting 07:00–07:30 (unpaid, R40,63) = 8.5 h × R81,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESOLVED</t>
+        </is>
+      </c>
+      <c r="B61" s="20">
+        <v>10033</v>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tsotlego Petrus Malakoane</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–14:00 Warehouse</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public holiday (Heritage Day) — owner to approve or decline</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLIC HOLIDAY — OWNER APPROVAL NEEDED: Tsotlego Petrus Malakoane worked 06:30–16:00 on 2026-09-24 (Heritage Day) at Warehouse (Normal). Public-holiday work is not paid automatically. Recommended: Petrus public holiday (Heritage Day): no fixed day — 9.5 h × R160 (R80 × 2) = R1 520,00. R0 is paid until the owner approves or declines.</t>
+        </is>
+      </c>
+      <c r="H61" s="20"/>
+      <c r="I61" s="21">
         <v>7.5</v>
       </c>
-      <c r="J60" s="18">
+      <c r="J61" s="21">
         <v>7</v>
       </c>
-      <c r="K60" s="17" t="inlineStr">
+      <c r="K61" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">approve adjusted</t>
         </is>
       </c>
-      <c r="L60" s="17" t="inlineStr">
+      <c r="L61" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernie Burness</t>
         </is>
       </c>
-      <c r="M60" s="17" t="inlineStr">
+      <c r="M61" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-23 11:02:04</t>
         </is>
       </c>
-      <c r="N60" s="17" t="inlineStr">
+      <c r="N61" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Public holiday (Heritage Day) approved by Bernie Burness 23 Sep — hours set to 06:30–14:00, meeting deducted: 7 h × R160 = R1 120,00. Owner not 100% sure of the end time — CONFIRM NEXT WEEK.</t>
         </is>
@@ -15400,10 +15745,10 @@
         </is>
       </c>
       <c r="C29" s="16">
-        <f>'Wage Detail Linked'!O62</f>
+        <f>'Wage Detail Linked'!O64</f>
       </c>
       <c r="D29" s="19">
-        <f>IF('Wage Detail Linked'!O62=0,IF(C29&gt;0,ROUND(C29*95,2),0),ROUND('Wage Detail Linked'!R62*C29/'Wage Detail Linked'!O62,2))</f>
+        <f>IF('Wage Detail Linked'!O64=0,IF(C29&gt;0,ROUND(C29*95,2),0),ROUND('Wage Detail Linked'!R64*C29/'Wage Detail Linked'!O64,2))</f>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -15424,10 +15769,10 @@
         </is>
       </c>
       <c r="C30" s="16">
-        <f>'Wage Detail Linked'!O63</f>
+        <f>'Wage Detail Linked'!O65</f>
       </c>
       <c r="D30" s="19">
-        <f>IF('Wage Detail Linked'!O63=0,IF(C30&gt;0,ROUND(C30*95,2),0),ROUND('Wage Detail Linked'!R63*C30/'Wage Detail Linked'!O63,2))</f>
+        <f>IF('Wage Detail Linked'!O65=0,IF(C30&gt;0,ROUND(C30*95,2),0),ROUND('Wage Detail Linked'!R65*C30/'Wage Detail Linked'!O65,2))</f>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
@@ -15448,10 +15793,10 @@
         </is>
       </c>
       <c r="C31" s="16">
-        <f>'Wage Detail Linked'!O64</f>
+        <f>'Wage Detail Linked'!O66</f>
       </c>
       <c r="D31" s="19">
-        <f>IF('Wage Detail Linked'!O64=0,IF(C31&gt;0,ROUND(C31*95,2),0),ROUND('Wage Detail Linked'!R64*C31/'Wage Detail Linked'!O64,2))</f>
+        <f>IF('Wage Detail Linked'!O66=0,IF(C31&gt;0,ROUND(C31*95,2),0),ROUND('Wage Detail Linked'!R66*C31/'Wage Detail Linked'!O66,2))</f>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
@@ -15485,10 +15830,10 @@
         </is>
       </c>
       <c r="C34" s="16">
-        <f>'Wage Detail Linked'!O70</f>
+        <f>'Wage Detail Linked'!O72</f>
       </c>
       <c r="D34" s="22">
-        <f>IF('Wage Detail Linked'!O70=0,IF(C34&gt;0,ROUND(C34*95,2),0),ROUND('Wage Detail Linked'!R70*C34/'Wage Detail Linked'!O70,2))</f>
+        <f>IF('Wage Detail Linked'!O72=0,IF(C34&gt;0,ROUND(C34*95,2),0),ROUND('Wage Detail Linked'!R72*C34/'Wage Detail Linked'!O72,2))</f>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -15509,10 +15854,10 @@
         </is>
       </c>
       <c r="C35" s="16">
-        <f>'Wage Detail Linked'!O71</f>
+        <f>'Wage Detail Linked'!O73</f>
       </c>
       <c r="D35" s="22">
-        <f>IF('Wage Detail Linked'!O71=0,IF(C35&gt;0,ROUND(C35*95,2),0),ROUND('Wage Detail Linked'!R71*C35/'Wage Detail Linked'!O71,2))</f>
+        <f>IF('Wage Detail Linked'!O73=0,IF(C35&gt;0,ROUND(C35*95,2),0),ROUND('Wage Detail Linked'!R73*C35/'Wage Detail Linked'!O73,2))</f>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
@@ -15546,10 +15891,10 @@
         </is>
       </c>
       <c r="C38" s="16">
-        <f>'Wage Detail Linked'!O77</f>
+        <f>'Wage Detail Linked'!O79</f>
       </c>
       <c r="D38" s="25">
-        <f>IF('Wage Detail Linked'!O77=0,IF(C38&gt;0,ROUND(C38*95,2),0),ROUND('Wage Detail Linked'!R77*C38/'Wage Detail Linked'!O77,2))</f>
+        <f>IF('Wage Detail Linked'!O79=0,IF(C38&gt;0,ROUND(C38*95,2),0),ROUND('Wage Detail Linked'!R79*C38/'Wage Detail Linked'!O79,2))</f>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
@@ -15583,10 +15928,10 @@
         </is>
       </c>
       <c r="C41" s="16">
-        <f>'Wage Detail Linked'!O89</f>
+        <f>'Wage Detail Linked'!O91</f>
       </c>
       <c r="D41" s="28">
-        <f>IF('Wage Detail Linked'!O89=0,IF(C41&gt;0,ROUND(C41*95,2),0),ROUND('Wage Detail Linked'!R89*C41/'Wage Detail Linked'!O89,2))</f>
+        <f>IF('Wage Detail Linked'!O91=0,IF(C41&gt;0,ROUND(C41*95,2),0),ROUND('Wage Detail Linked'!R91*C41/'Wage Detail Linked'!O91,2))</f>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>

--- a/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
+++ b/docs/BW_Payroll_2026-09-19_to_25_AUDITOR.xlsx
@@ -6656,18 +6656,18 @@
         <f>IF(N80&lt;&gt;"",N80,M80)</f>
       </c>
       <c r="P80" s="4">
-        <v>450</v>
+        <v>684</v>
       </c>
       <c r="Q80" s="7"/>
       <c r="R80" s="5">
         <f>IF(Q80&lt;&gt;"",Q80,IF(N80&lt;&gt;"",IF(M80&gt;0,ROUND(P80*N80/M80,2),0),P80))</f>
       </c>
       <c r="S80" s="9">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="T80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER CORRECTION: Owner 24 Sep: Sunday house work 08:00–14:00 = 6 h × R62,50 × 1.2 (Sunday) = 6 h × R75 = R450,00 (was R375 — Sunday ×1.2 had been left off)</t>
+          <t xml:space="preserve">OWNER CORRECTION: Owner 24 Sep: VENUE — installing lights at the House is event/venue work, not garden work. Sunday 08:00–14:00 = 6 h × R95 × 1.2 = 6 h × R114 = R684,00 (paid R375 on 23 Sep at the flat garden rate; corrected to R450 garden+Sunday, then to R684 venue+Sunday on 24 Sep)</t>
         </is>
       </c>
       <c r="U80" s="6"/>
